--- a/research/traditional_assets/database/data/argentina/argentina_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_shipbuilding_marine.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="G2">
-        <v>0.352</v>
+        <v>0.04508196721311476</v>
       </c>
       <c r="H2">
-        <v>0.352</v>
+        <v>0.04508196721311476</v>
       </c>
       <c r="I2">
-        <v>-0.28</v>
+        <v>-0.06229508196721312</v>
       </c>
       <c r="J2">
-        <v>-0.28</v>
+        <v>-0.04162988650693569</v>
       </c>
       <c r="K2">
-        <v>-1.4</v>
+        <v>-0.882</v>
       </c>
       <c r="L2">
-        <v>-0.3733333333333333</v>
+        <v>-0.1445901639344263</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,31 +630,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.01</v>
+        <v>4.41</v>
       </c>
       <c r="V2">
-        <v>0.2722826086956522</v>
+        <v>0.2308900523560209</v>
       </c>
       <c r="W2">
-        <v>-0.08641975308641975</v>
+        <v>-0.04927374301675978</v>
       </c>
       <c r="X2">
-        <v>0.3194409272501488</v>
+        <v>0.2291725556540588</v>
       </c>
       <c r="Y2">
-        <v>-0.4058606803365685</v>
+        <v>-0.2784462986708186</v>
       </c>
       <c r="Z2">
-        <v>0.3588516746411484</v>
+        <v>0.4891740176423416</v>
       </c>
       <c r="AA2">
-        <v>-0.1004784688995215</v>
+        <v>-0.02036425883659244</v>
       </c>
       <c r="AB2">
-        <v>0.3194409272501488</v>
+        <v>0.2291725556540588</v>
       </c>
       <c r="AC2">
-        <v>-0.4199193961496703</v>
+        <v>-0.2495368144906512</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -666,7 +666,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-5.01</v>
+        <v>-4.41</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -675,28 +675,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.3741598207617625</v>
+        <v>-0.3002042205582028</v>
       </c>
       <c r="AK2">
-        <v>-0.379833206974981</v>
+        <v>-0.3421256788207913</v>
       </c>
       <c r="AL2">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.175</v>
+        <v>-0.588</v>
       </c>
       <c r="AN2">
-        <v>-0</v>
-      </c>
-      <c r="AO2">
-        <v>-6.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP2">
-        <v>12.46268656716418</v>
+        <v>-10.99750623441397</v>
       </c>
       <c r="AQ2">
-        <v>-6.000000000000001</v>
+        <v>0.6462585034013606</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +713,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.47</v>
+        <v>0.472</v>
       </c>
       <c r="G3">
-        <v>0.352</v>
+        <v>0.04508196721311476</v>
       </c>
       <c r="H3">
-        <v>0.352</v>
+        <v>0.04508196721311476</v>
       </c>
       <c r="I3">
-        <v>-0.28</v>
+        <v>-0.06229508196721312</v>
       </c>
       <c r="J3">
-        <v>-0.28</v>
+        <v>-0.04162988650693569</v>
       </c>
       <c r="K3">
-        <v>-1.4</v>
+        <v>-0.882</v>
       </c>
       <c r="L3">
-        <v>-0.3733333333333333</v>
+        <v>-0.1445901639344263</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,31 +755,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.01</v>
+        <v>4.41</v>
       </c>
       <c r="V3">
-        <v>0.2722826086956522</v>
+        <v>0.2308900523560209</v>
       </c>
       <c r="W3">
-        <v>-0.08641975308641975</v>
+        <v>-0.04927374301675978</v>
       </c>
       <c r="X3">
-        <v>0.3194409272501488</v>
+        <v>0.2291725556540588</v>
       </c>
       <c r="Y3">
-        <v>-0.4058606803365685</v>
+        <v>-0.2784462986708186</v>
       </c>
       <c r="Z3">
-        <v>0.3588516746411484</v>
+        <v>0.4891740176423416</v>
       </c>
       <c r="AA3">
-        <v>-0.1004784688995215</v>
+        <v>-0.02036425883659244</v>
       </c>
       <c r="AB3">
-        <v>0.3194409272501488</v>
+        <v>0.2291725556540588</v>
       </c>
       <c r="AC3">
-        <v>-0.4199193961496703</v>
+        <v>-0.2495368144906512</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -794,7 +791,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5.01</v>
+        <v>-4.41</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -803,28 +800,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.3741598207617625</v>
+        <v>-0.3002042205582028</v>
       </c>
       <c r="AK3">
-        <v>-0.379833206974981</v>
+        <v>-0.3421256788207913</v>
       </c>
       <c r="AL3">
-        <v>0.175</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.175</v>
+        <v>-0.588</v>
       </c>
       <c r="AN3">
-        <v>-0</v>
-      </c>
-      <c r="AO3">
-        <v>-6.000000000000001</v>
+        <v>0</v>
       </c>
       <c r="AP3">
-        <v>12.46268656716418</v>
+        <v>-10.99750623441397</v>
       </c>
       <c r="AQ3">
-        <v>-6.000000000000001</v>
+        <v>0.6462585034013606</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/argentina/argentina_shipbuilding_marine.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_shipbuilding_marine.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.2207230632538978</v>
+        <v>0.2199797825325092</v>
       </c>
       <c r="C2">
-        <v>34.8</v>
+        <v>34.58740203660123</v>
       </c>
       <c r="D2">
-        <v>31.73</v>
+        <v>31.86540203660123</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.348</v>
       </c>
       <c r="G2">
         <v>3.07</v>
@@ -1445,28 +1445,28 @@
         <v>0.606</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0175044</v>
       </c>
       <c r="N2">
-        <v>0.606</v>
+        <v>0.5884956</v>
       </c>
       <c r="O2">
-        <v>0.2121</v>
+        <v>0.20597346</v>
       </c>
       <c r="P2">
-        <v>0.3939</v>
+        <v>0.38252214</v>
       </c>
       <c r="Q2">
-        <v>0.8179000000000001</v>
+        <v>0.80652214</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.2207230632538978</v>
+        <v>0.2218715480126356</v>
       </c>
       <c r="T2">
-        <v>0.8594621135367391</v>
+        <v>0.8651050466054148</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>34.61986700486735</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.2199797825325092</v>
+        <v>0.2192365018111206</v>
       </c>
       <c r="C3">
-        <v>34.58740203660123</v>
+        <v>34.37596463308913</v>
       </c>
       <c r="D3">
-        <v>31.86540203660123</v>
+        <v>32.00196463308912</v>
       </c>
       <c r="E3">
-        <v>0.348</v>
+        <v>0.696</v>
       </c>
       <c r="F3">
-        <v>0.348</v>
+        <v>0.696</v>
       </c>
       <c r="G3">
         <v>3.07</v>
@@ -1527,28 +1527,28 @@
         <v>0.606</v>
       </c>
       <c r="M3">
-        <v>0.0175044</v>
+        <v>0.03500879999999999</v>
       </c>
       <c r="N3">
-        <v>0.5884956</v>
+        <v>0.5709912</v>
       </c>
       <c r="O3">
-        <v>0.20597346</v>
+        <v>0.19984692</v>
       </c>
       <c r="P3">
-        <v>0.38252214</v>
+        <v>0.37114428</v>
       </c>
       <c r="Q3">
-        <v>0.80652214</v>
+        <v>0.79514428</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.2218715480126356</v>
+        <v>0.2230434712358373</v>
       </c>
       <c r="T3">
-        <v>0.8651050466054148</v>
+        <v>0.8708631415734509</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>34.61986700486735</v>
+        <v>17.30993350243368</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.2192365018111206</v>
+        <v>0.2185224710897319</v>
       </c>
       <c r="C4">
-        <v>34.37596463308913</v>
+        <v>34.16026001856302</v>
       </c>
       <c r="D4">
-        <v>32.00196463308912</v>
+        <v>32.13426001856302</v>
       </c>
       <c r="E4">
-        <v>0.696</v>
+        <v>1.044</v>
       </c>
       <c r="F4">
-        <v>0.696</v>
+        <v>1.044</v>
       </c>
       <c r="G4">
         <v>3.07</v>
@@ -1609,45 +1609,45 @@
         <v>0.606</v>
       </c>
       <c r="M4">
-        <v>0.03500879999999999</v>
+        <v>0.05407919999999999</v>
       </c>
       <c r="N4">
-        <v>0.5709912</v>
+        <v>0.5519208</v>
       </c>
       <c r="O4">
-        <v>0.19984692</v>
+        <v>0.19317228</v>
       </c>
       <c r="P4">
-        <v>0.37114428</v>
+        <v>0.35874852</v>
       </c>
       <c r="Q4">
-        <v>0.79514428</v>
+        <v>0.7827485200000001</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.2230434712358373</v>
+        <v>0.2242395578244659</v>
       </c>
       <c r="T4">
-        <v>0.8708631415734509</v>
+        <v>0.8767399601490755</v>
       </c>
       <c r="U4">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V4">
         <v>0.35</v>
       </c>
       <c r="W4">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y4">
-        <v>17.30993350243368</v>
+        <v>11.20578706785604</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.2185224710897319</v>
+        <v>0.2178331403683433</v>
       </c>
       <c r="C5">
-        <v>34.16026001856302</v>
+        <v>33.94102086424925</v>
       </c>
       <c r="D5">
-        <v>32.13426001856302</v>
+        <v>32.26302086424925</v>
       </c>
       <c r="E5">
-        <v>1.044</v>
+        <v>1.392</v>
       </c>
       <c r="F5">
-        <v>1.044</v>
+        <v>1.392</v>
       </c>
       <c r="G5">
         <v>3.07</v>
@@ -1691,45 +1691,45 @@
         <v>0.606</v>
       </c>
       <c r="M5">
-        <v>0.05407919999999999</v>
+        <v>0.074472</v>
       </c>
       <c r="N5">
-        <v>0.5519208</v>
+        <v>0.531528</v>
       </c>
       <c r="O5">
-        <v>0.19317228</v>
+        <v>0.1860348</v>
       </c>
       <c r="P5">
-        <v>0.35874852</v>
+        <v>0.3454932</v>
       </c>
       <c r="Q5">
-        <v>0.7827485200000001</v>
+        <v>0.7694932000000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.2242395578244659</v>
+        <v>0.2254605628836909</v>
       </c>
       <c r="T5">
-        <v>0.8767399601490755</v>
+        <v>0.8827392124450257</v>
       </c>
       <c r="U5">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V5">
         <v>0.35</v>
       </c>
       <c r="W5">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y5">
-        <v>11.20578706785604</v>
+        <v>8.137286496938447</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.2178331403683433</v>
+        <v>0.2171366596469546</v>
       </c>
       <c r="C6">
-        <v>33.94102086424925</v>
+        <v>33.7241695168027</v>
       </c>
       <c r="D6">
-        <v>32.26302086424925</v>
+        <v>32.3941695168027</v>
       </c>
       <c r="E6">
-        <v>1.392</v>
+        <v>1.74</v>
       </c>
       <c r="F6">
-        <v>1.392</v>
+        <v>1.74</v>
       </c>
       <c r="G6">
         <v>3.07</v>
@@ -1773,45 +1773,45 @@
         <v>0.606</v>
       </c>
       <c r="M6">
-        <v>0.074472</v>
+        <v>0.094482</v>
       </c>
       <c r="N6">
-        <v>0.531528</v>
+        <v>0.511518</v>
       </c>
       <c r="O6">
-        <v>0.1860348</v>
+        <v>0.1790313</v>
       </c>
       <c r="P6">
-        <v>0.3454932</v>
+        <v>0.3324867</v>
       </c>
       <c r="Q6">
-        <v>0.7694932000000001</v>
+        <v>0.7564867000000001</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.2254605628836909</v>
+        <v>0.2267072733125838</v>
       </c>
       <c r="T6">
-        <v>0.8827392124450257</v>
+        <v>0.8888647647893118</v>
       </c>
       <c r="U6">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V6">
         <v>0.35</v>
       </c>
       <c r="W6">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y6">
-        <v>8.137286496938447</v>
+        <v>6.413920111767322</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.2171366596469546</v>
+        <v>0.216458378925566</v>
       </c>
       <c r="C7">
-        <v>33.7241695168027</v>
+        <v>33.50491995265576</v>
       </c>
       <c r="D7">
-        <v>32.3941695168027</v>
+        <v>32.52291995265576</v>
       </c>
       <c r="E7">
-        <v>1.74</v>
+        <v>2.088</v>
       </c>
       <c r="F7">
-        <v>1.74</v>
+        <v>2.088</v>
       </c>
       <c r="G7">
         <v>3.07</v>
@@ -1855,45 +1855,45 @@
         <v>0.606</v>
       </c>
       <c r="M7">
-        <v>0.094482</v>
+        <v>0.1154664</v>
       </c>
       <c r="N7">
-        <v>0.511518</v>
+        <v>0.4905336</v>
       </c>
       <c r="O7">
-        <v>0.1790313</v>
+        <v>0.17168676</v>
       </c>
       <c r="P7">
-        <v>0.3324867</v>
+        <v>0.31884684</v>
       </c>
       <c r="Q7">
-        <v>0.7564867000000001</v>
+        <v>0.74284684</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.2267072733125838</v>
+        <v>0.227980509495283</v>
       </c>
       <c r="T7">
-        <v>0.8888647647893118</v>
+        <v>0.8951206480345399</v>
       </c>
       <c r="U7">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V7">
         <v>0.35</v>
       </c>
       <c r="W7">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y7">
-        <v>6.413920111767322</v>
+        <v>5.248280019122445</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.216458378925566</v>
+        <v>0.2158613482041773</v>
       </c>
       <c r="C8">
-        <v>33.50491995265576</v>
+        <v>33.27109746898174</v>
       </c>
       <c r="D8">
-        <v>32.52291995265576</v>
+        <v>32.63709746898174</v>
       </c>
       <c r="E8">
-        <v>2.088</v>
+        <v>2.435999999999999</v>
       </c>
       <c r="F8">
-        <v>2.088</v>
+        <v>2.435999999999999</v>
       </c>
       <c r="G8">
         <v>3.07</v>
@@ -1937,45 +1937,45 @@
         <v>0.606</v>
       </c>
       <c r="M8">
-        <v>0.1154664</v>
+        <v>0.1408008</v>
       </c>
       <c r="N8">
-        <v>0.4905336</v>
+        <v>0.4651992</v>
       </c>
       <c r="O8">
-        <v>0.17168676</v>
+        <v>0.16281972</v>
       </c>
       <c r="P8">
-        <v>0.31884684</v>
+        <v>0.30237948</v>
       </c>
       <c r="Q8">
-        <v>0.7428468400000001</v>
+        <v>0.7263794800000001</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.227980509495283</v>
+        <v>0.2292811271012659</v>
       </c>
       <c r="T8">
-        <v>0.8951206480345399</v>
+        <v>0.9015110664033213</v>
       </c>
       <c r="U8">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V8">
         <v>0.35</v>
       </c>
       <c r="W8">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y8">
-        <v>5.248280019122447</v>
+        <v>4.303952818449896</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.2158613482041773</v>
+        <v>0.2153488174827887</v>
       </c>
       <c r="C9">
-        <v>33.27109746898174</v>
+        <v>33.02175645910714</v>
       </c>
       <c r="D9">
-        <v>32.63709746898174</v>
+        <v>32.73575645910714</v>
       </c>
       <c r="E9">
-        <v>2.436</v>
+        <v>2.784</v>
       </c>
       <c r="F9">
-        <v>2.436</v>
+        <v>2.784</v>
       </c>
       <c r="G9">
         <v>3.07</v>
@@ -2019,45 +2019,45 @@
         <v>0.606</v>
       </c>
       <c r="M9">
-        <v>0.1408008</v>
+        <v>0.1706592</v>
       </c>
       <c r="N9">
-        <v>0.4651992</v>
+        <v>0.4353408</v>
       </c>
       <c r="O9">
-        <v>0.16281972</v>
+        <v>0.15236928</v>
       </c>
       <c r="P9">
-        <v>0.30237948</v>
+        <v>0.28297152</v>
       </c>
       <c r="Q9">
-        <v>0.7263794800000001</v>
+        <v>0.7069715200000001</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.2292811271012659</v>
+        <v>0.2306100190030312</v>
       </c>
       <c r="T9">
-        <v>0.9015110664033213</v>
+        <v>0.9080404069105547</v>
       </c>
       <c r="U9">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V9">
         <v>0.35</v>
       </c>
       <c r="W9">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y9">
-        <v>4.303952818449895</v>
+        <v>3.550936603476402</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.2153488174827887</v>
+        <v>0.2148408367614001</v>
       </c>
       <c r="C10">
-        <v>33.02175645910714</v>
+        <v>32.77212992613376</v>
       </c>
       <c r="D10">
-        <v>32.73575645910714</v>
+        <v>32.83412992613376</v>
       </c>
       <c r="E10">
-        <v>2.784</v>
+        <v>3.132</v>
       </c>
       <c r="F10">
-        <v>2.784</v>
+        <v>3.132</v>
       </c>
       <c r="G10">
         <v>3.07</v>
@@ -2101,45 +2101,45 @@
         <v>0.606</v>
       </c>
       <c r="M10">
-        <v>0.1706592</v>
+        <v>0.2007612</v>
       </c>
       <c r="N10">
-        <v>0.4353408</v>
+        <v>0.4052388</v>
       </c>
       <c r="O10">
-        <v>0.15236928</v>
+        <v>0.14183358</v>
       </c>
       <c r="P10">
-        <v>0.28297152</v>
+        <v>0.26340522</v>
       </c>
       <c r="Q10">
-        <v>0.7069715200000001</v>
+        <v>0.68740522</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.2306100190030312</v>
+        <v>0.2319681173202199</v>
       </c>
       <c r="T10">
-        <v>0.9080404069105547</v>
+        <v>0.914713249406958</v>
       </c>
       <c r="U10">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V10">
         <v>0.35</v>
       </c>
       <c r="W10">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y10">
-        <v>3.550936603476402</v>
+        <v>3.018511545059503</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.2148408367614001</v>
+        <v>0.2149477560400114</v>
       </c>
       <c r="C11">
-        <v>32.77212992613376</v>
+        <v>32.40337528198286</v>
       </c>
       <c r="D11">
-        <v>32.83412992613376</v>
+        <v>32.81337528198286</v>
       </c>
       <c r="E11">
-        <v>3.132</v>
+        <v>3.48</v>
       </c>
       <c r="F11">
-        <v>3.132</v>
+        <v>3.48</v>
       </c>
       <c r="G11">
         <v>3.07</v>
@@ -2183,45 +2183,45 @@
         <v>0.606</v>
       </c>
       <c r="M11">
-        <v>0.2007612</v>
+        <v>0.263784</v>
       </c>
       <c r="N11">
-        <v>0.4052388</v>
+        <v>0.342216</v>
       </c>
       <c r="O11">
-        <v>0.14183358</v>
+        <v>0.1197756</v>
       </c>
       <c r="P11">
-        <v>0.26340522</v>
+        <v>0.2224404</v>
       </c>
       <c r="Q11">
-        <v>0.68740522</v>
+        <v>0.6464404000000001</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.2319681173202199</v>
+        <v>0.2333563956000127</v>
       </c>
       <c r="T11">
-        <v>0.914713249406958</v>
+        <v>0.9215343772921702</v>
       </c>
       <c r="U11">
-        <v>0.0641</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.04166500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y11">
-        <v>3.018511545059503</v>
+        <v>2.297334182512965</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.2149477560400114</v>
+        <v>0.2143702253186228</v>
       </c>
       <c r="C12">
-        <v>32.40337528198286</v>
+        <v>32.16779568280975</v>
       </c>
       <c r="D12">
-        <v>32.81337528198286</v>
+        <v>32.92579568280975</v>
       </c>
       <c r="E12">
-        <v>3.48</v>
+        <v>3.828</v>
       </c>
       <c r="F12">
-        <v>3.48</v>
+        <v>3.828</v>
       </c>
       <c r="G12">
         <v>3.07</v>
@@ -2265,28 +2265,28 @@
         <v>0.606</v>
       </c>
       <c r="M12">
-        <v>0.263784</v>
+        <v>0.2901624</v>
       </c>
       <c r="N12">
-        <v>0.342216</v>
+        <v>0.3158376</v>
       </c>
       <c r="O12">
-        <v>0.1197756</v>
+        <v>0.11054316</v>
       </c>
       <c r="P12">
-        <v>0.2224404</v>
+        <v>0.20529444</v>
       </c>
       <c r="Q12">
-        <v>0.6464404</v>
+        <v>0.62929444</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.2333563956000127</v>
+        <v>0.23477587114452</v>
       </c>
       <c r="T12">
-        <v>0.9215343772921702</v>
+        <v>0.9285087889500839</v>
       </c>
       <c r="U12">
         <v>0.07580000000000001</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>2.297334182512965</v>
+        <v>2.088485620466332</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.2143702253186228</v>
+        <v>0.2149002945972341</v>
       </c>
       <c r="C13">
-        <v>32.16779568280975</v>
+        <v>31.71658502426619</v>
       </c>
       <c r="D13">
-        <v>32.92579568280975</v>
+        <v>32.82258502426619</v>
       </c>
       <c r="E13">
-        <v>3.828</v>
+        <v>4.175999999999999</v>
       </c>
       <c r="F13">
-        <v>3.828</v>
+        <v>4.175999999999999</v>
       </c>
       <c r="G13">
         <v>3.07</v>
@@ -2347,45 +2347,45 @@
         <v>0.606</v>
       </c>
       <c r="M13">
-        <v>0.2901624</v>
+        <v>0.3758399999999999</v>
       </c>
       <c r="N13">
-        <v>0.3158376</v>
+        <v>0.2301600000000001</v>
       </c>
       <c r="O13">
-        <v>0.11054316</v>
+        <v>0.08055600000000003</v>
       </c>
       <c r="P13">
-        <v>0.20529444</v>
+        <v>0.1496040000000001</v>
       </c>
       <c r="Q13">
-        <v>0.62929444</v>
+        <v>0.5736040000000001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.23477587114452</v>
+        <v>0.236227607496857</v>
       </c>
       <c r="T13">
-        <v>0.9285087889500839</v>
+        <v>0.9356417099638591</v>
       </c>
       <c r="U13">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V13">
         <v>0.35</v>
       </c>
       <c r="W13">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y13">
-        <v>2.088485620466332</v>
+        <v>1.612388250319285</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.2149002945972341</v>
+        <v>0.2204957975792463</v>
       </c>
       <c r="C14">
-        <v>31.71658502426619</v>
+        <v>30.31727826746044</v>
       </c>
       <c r="D14">
-        <v>32.82258502426619</v>
+        <v>31.77127826746044</v>
       </c>
       <c r="E14">
-        <v>4.175999999999999</v>
+        <v>4.524</v>
       </c>
       <c r="F14">
-        <v>4.175999999999999</v>
+        <v>4.524</v>
       </c>
       <c r="G14">
         <v>3.07</v>
@@ -2429,45 +2429,45 @@
         <v>0.606</v>
       </c>
       <c r="M14">
-        <v>0.3758399999999999</v>
+        <v>0.6641232</v>
       </c>
       <c r="N14">
-        <v>0.2301600000000001</v>
+        <v>-0.05812320000000004</v>
       </c>
       <c r="O14">
-        <v>0.08055600000000003</v>
+        <v>-0.02034312000000001</v>
       </c>
       <c r="P14">
-        <v>0.1496040000000001</v>
+        <v>-0.03778008000000003</v>
       </c>
       <c r="Q14">
-        <v>0.5736040000000001</v>
+        <v>0.38621992</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.236227607496857</v>
+        <v>0.2385133622591417</v>
       </c>
       <c r="T14">
-        <v>0.9356417099638591</v>
+        <v>0.9468724738349925</v>
       </c>
       <c r="U14">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V14">
-        <v>0.35</v>
+        <v>0.3193684545277141</v>
       </c>
       <c r="W14">
-        <v>0.0585</v>
+        <v>0.09991671087533158</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y14">
-        <v>1.612388250319285</v>
+        <v>0.9124812986506118</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.2204957975792463</v>
+        <v>0.2215057975792463</v>
       </c>
       <c r="C15">
-        <v>30.31727826746044</v>
+        <v>29.78664917102631</v>
       </c>
       <c r="D15">
-        <v>31.77127826746044</v>
+        <v>31.58864917102632</v>
       </c>
       <c r="E15">
-        <v>4.524</v>
+        <v>4.872</v>
       </c>
       <c r="F15">
-        <v>4.524</v>
+        <v>4.872</v>
       </c>
       <c r="G15">
         <v>3.07</v>
@@ -2511,37 +2511,37 @@
         <v>0.606</v>
       </c>
       <c r="M15">
-        <v>0.6641232</v>
+        <v>0.7152096</v>
       </c>
       <c r="N15">
-        <v>-0.05812320000000004</v>
+        <v>-0.1092096</v>
       </c>
       <c r="O15">
-        <v>-0.02034312000000001</v>
+        <v>-0.03822336</v>
       </c>
       <c r="P15">
-        <v>-0.03778008000000003</v>
+        <v>-0.07098624000000001</v>
       </c>
       <c r="Q15">
-        <v>0.38621992</v>
+        <v>0.3530137600000001</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2385133622591417</v>
+        <v>0.2407542153086666</v>
       </c>
       <c r="T15">
-        <v>0.9468724738349925</v>
+        <v>0.9578826188795855</v>
       </c>
       <c r="U15">
         <v>0.1468</v>
       </c>
       <c r="V15">
-        <v>0.3193684545277141</v>
+        <v>0.2965564220614488</v>
       </c>
       <c r="W15">
-        <v>0.09991671087533158</v>
+        <v>0.1032655172413793</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.9124812986506118</v>
+        <v>0.8473040630327109</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.2215057975792463</v>
+        <v>0.2325688436787285</v>
       </c>
       <c r="C16">
-        <v>29.78664917102631</v>
+        <v>27.56753043882188</v>
       </c>
       <c r="D16">
-        <v>31.58864917102632</v>
+        <v>29.71753043882188</v>
       </c>
       <c r="E16">
-        <v>4.872</v>
+        <v>5.220000000000001</v>
       </c>
       <c r="F16">
-        <v>4.872</v>
+        <v>5.220000000000001</v>
       </c>
       <c r="G16">
         <v>3.07</v>
@@ -2593,45 +2593,45 @@
         <v>0.606</v>
       </c>
       <c r="M16">
-        <v>0.7152096</v>
+        <v>1.048176</v>
       </c>
       <c r="N16">
-        <v>-0.1092096</v>
+        <v>-0.4421760000000002</v>
       </c>
       <c r="O16">
-        <v>-0.03822336</v>
+        <v>-0.1547616000000001</v>
       </c>
       <c r="P16">
-        <v>-0.07098624000000001</v>
+        <v>-0.2874144000000002</v>
       </c>
       <c r="Q16">
-        <v>0.3530137600000001</v>
+        <v>0.1365855999999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2407542153086666</v>
+        <v>0.2453454956058063</v>
       </c>
       <c r="T16">
-        <v>0.9578826188795855</v>
+        <v>0.9804412877858789</v>
       </c>
       <c r="U16">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V16">
-        <v>0.2965564220614488</v>
+        <v>0.2023515134862847</v>
       </c>
       <c r="W16">
-        <v>0.1032655172413793</v>
+        <v>0.160167816091954</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y16">
-        <v>0.8473040630327109</v>
+        <v>0.5781471813893848</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.2325688436787284</v>
+        <v>0.2341188436787284</v>
       </c>
       <c r="C17">
-        <v>27.56753043882188</v>
+        <v>26.97493371509329</v>
       </c>
       <c r="D17">
-        <v>29.71753043882188</v>
+        <v>29.47293371509329</v>
       </c>
       <c r="E17">
-        <v>5.22</v>
+        <v>5.568</v>
       </c>
       <c r="F17">
-        <v>5.22</v>
+        <v>5.568</v>
       </c>
       <c r="G17">
         <v>3.07</v>
@@ -2675,37 +2675,37 @@
         <v>0.606</v>
       </c>
       <c r="M17">
-        <v>1.048176</v>
+        <v>1.1180544</v>
       </c>
       <c r="N17">
-        <v>-0.442176</v>
+        <v>-0.5120543999999999</v>
       </c>
       <c r="O17">
-        <v>-0.1547616</v>
+        <v>-0.17921904</v>
       </c>
       <c r="P17">
-        <v>-0.2874144</v>
+        <v>-0.3328353599999999</v>
       </c>
       <c r="Q17">
-        <v>0.1365856</v>
+        <v>0.09116464000000013</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2453454956058063</v>
+        <v>0.2477210372201611</v>
       </c>
       <c r="T17">
-        <v>0.9804412877858788</v>
+        <v>0.9921132078785678</v>
       </c>
       <c r="U17">
         <v>0.2008</v>
       </c>
       <c r="V17">
-        <v>0.2023515134862847</v>
+        <v>0.1897045438933919</v>
       </c>
       <c r="W17">
-        <v>0.160167816091954</v>
+        <v>0.1627073275862069</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.578147181389385</v>
+        <v>0.5420129825525485</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.2341188436787284</v>
+        <v>0.2356688436787285</v>
       </c>
       <c r="C18">
-        <v>26.97493371509329</v>
+        <v>26.38633053674511</v>
       </c>
       <c r="D18">
-        <v>29.47293371509329</v>
+        <v>29.23233053674511</v>
       </c>
       <c r="E18">
-        <v>5.568</v>
+        <v>5.916</v>
       </c>
       <c r="F18">
-        <v>5.568</v>
+        <v>5.916</v>
       </c>
       <c r="G18">
         <v>3.07</v>
@@ -2757,37 +2757,37 @@
         <v>0.606</v>
       </c>
       <c r="M18">
-        <v>1.1180544</v>
+        <v>1.1879328</v>
       </c>
       <c r="N18">
-        <v>-0.5120543999999999</v>
+        <v>-0.5819328</v>
       </c>
       <c r="O18">
-        <v>-0.17921904</v>
+        <v>-0.20367648</v>
       </c>
       <c r="P18">
-        <v>-0.3328353599999999</v>
+        <v>-0.37825632</v>
       </c>
       <c r="Q18">
-        <v>0.09116464000000013</v>
+        <v>0.04574368000000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2477210372201611</v>
+        <v>0.2501538208011269</v>
       </c>
       <c r="T18">
-        <v>0.9921132078785678</v>
+        <v>1.004066379057828</v>
       </c>
       <c r="U18">
         <v>0.2008</v>
       </c>
       <c r="V18">
-        <v>0.1897045438933919</v>
+        <v>0.1785454530761336</v>
       </c>
       <c r="W18">
-        <v>0.1627073275862069</v>
+        <v>0.1649480730223124</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.5420129825525485</v>
+        <v>0.5101298659318103</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.2356688436787285</v>
+        <v>0.2443069213700503</v>
       </c>
       <c r="C19">
-        <v>26.38633053674511</v>
+        <v>24.766278456485</v>
       </c>
       <c r="D19">
-        <v>29.23233053674511</v>
+        <v>27.960278456485</v>
       </c>
       <c r="E19">
-        <v>5.916</v>
+        <v>6.264</v>
       </c>
       <c r="F19">
-        <v>5.916</v>
+        <v>6.264</v>
       </c>
       <c r="G19">
         <v>3.07</v>
@@ -2839,45 +2839,45 @@
         <v>0.606</v>
       </c>
       <c r="M19">
-        <v>1.1879328</v>
+        <v>1.4770512</v>
       </c>
       <c r="N19">
-        <v>-0.5819328</v>
+        <v>-0.8710512</v>
       </c>
       <c r="O19">
-        <v>-0.20367648</v>
+        <v>-0.30486792</v>
       </c>
       <c r="P19">
-        <v>-0.37825632</v>
+        <v>-0.56618328</v>
       </c>
       <c r="Q19">
-        <v>0.04574368000000001</v>
+        <v>-0.1421832799999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2501538208011269</v>
+        <v>0.2536070109222648</v>
       </c>
       <c r="T19">
-        <v>1.004066379057828</v>
+        <v>1.021033187349137</v>
       </c>
       <c r="U19">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.1785454530761336</v>
+        <v>0.1435969179673663</v>
       </c>
       <c r="W19">
-        <v>0.1649480730223124</v>
+        <v>0.201939846743295</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y19">
-        <v>0.5101298659318103</v>
+        <v>0.4102769084781895</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.2443069213700503</v>
+        <v>0.2462069213700503</v>
       </c>
       <c r="C20">
-        <v>24.766278456485</v>
+        <v>24.15319515145669</v>
       </c>
       <c r="D20">
-        <v>27.960278456485</v>
+        <v>27.69519515145668</v>
       </c>
       <c r="E20">
-        <v>6.263999999999999</v>
+        <v>6.611999999999999</v>
       </c>
       <c r="F20">
-        <v>6.263999999999999</v>
+        <v>6.611999999999999</v>
       </c>
       <c r="G20">
         <v>3.07</v>
@@ -2921,37 +2921,37 @@
         <v>0.606</v>
       </c>
       <c r="M20">
-        <v>1.4770512</v>
+        <v>1.5591096</v>
       </c>
       <c r="N20">
-        <v>-0.8710512</v>
+        <v>-0.9531096</v>
       </c>
       <c r="O20">
-        <v>-0.30486792</v>
+        <v>-0.33358836</v>
       </c>
       <c r="P20">
-        <v>-0.56618328</v>
+        <v>-0.6195212400000001</v>
       </c>
       <c r="Q20">
-        <v>-0.1421832799999999</v>
+        <v>-0.19552124</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2536070109222648</v>
+        <v>0.2561725295756261</v>
       </c>
       <c r="T20">
-        <v>1.021033187349137</v>
+        <v>1.033638535341101</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.1435969179673663</v>
+        <v>0.1360391854427681</v>
       </c>
       <c r="W20">
-        <v>0.201939846743295</v>
+        <v>0.2037219600725953</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.4102769084781895</v>
+        <v>0.3886833869793375</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.2462069213700503</v>
+        <v>0.2481069213700503</v>
       </c>
       <c r="C21">
-        <v>24.15319515145669</v>
+        <v>23.54509099668327</v>
       </c>
       <c r="D21">
-        <v>27.69519515145668</v>
+        <v>27.43509099668327</v>
       </c>
       <c r="E21">
-        <v>6.611999999999999</v>
+        <v>6.96</v>
       </c>
       <c r="F21">
-        <v>6.611999999999999</v>
+        <v>6.96</v>
       </c>
       <c r="G21">
         <v>3.07</v>
@@ -3003,37 +3003,37 @@
         <v>0.606</v>
       </c>
       <c r="M21">
-        <v>1.5591096</v>
+        <v>1.641168</v>
       </c>
       <c r="N21">
-        <v>-0.9531096</v>
+        <v>-1.035168</v>
       </c>
       <c r="O21">
-        <v>-0.33358836</v>
+        <v>-0.3623088</v>
       </c>
       <c r="P21">
-        <v>-0.6195212400000001</v>
+        <v>-0.6728592000000001</v>
       </c>
       <c r="Q21">
-        <v>-0.19552124</v>
+        <v>-0.2488592000000001</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2561725295756261</v>
+        <v>0.2588021861953215</v>
       </c>
       <c r="T21">
-        <v>1.033638535341101</v>
+        <v>1.046559017032865</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.1360391854427681</v>
+        <v>0.1292372261706297</v>
       </c>
       <c r="W21">
-        <v>0.2037219600725953</v>
+        <v>0.2053258620689655</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.3886833869793375</v>
+        <v>0.3692492176303704</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.2481069213700503</v>
+        <v>0.2500069213700503</v>
       </c>
       <c r="C22">
-        <v>23.54509099668327</v>
+        <v>22.94182700982145</v>
       </c>
       <c r="D22">
-        <v>27.43509099668327</v>
+        <v>27.17982700982145</v>
       </c>
       <c r="E22">
-        <v>6.96</v>
+        <v>7.308</v>
       </c>
       <c r="F22">
-        <v>6.96</v>
+        <v>7.308</v>
       </c>
       <c r="G22">
         <v>3.07</v>
@@ -3085,37 +3085,37 @@
         <v>0.606</v>
       </c>
       <c r="M22">
-        <v>1.641168</v>
+        <v>1.7232264</v>
       </c>
       <c r="N22">
-        <v>-1.035168</v>
+        <v>-1.1172264</v>
       </c>
       <c r="O22">
-        <v>-0.3623088</v>
+        <v>-0.3910292399999999</v>
       </c>
       <c r="P22">
-        <v>-0.6728592000000001</v>
+        <v>-0.7261971599999999</v>
       </c>
       <c r="Q22">
-        <v>-0.2488592000000001</v>
+        <v>-0.3021971599999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2588021861953215</v>
+        <v>0.2614984164003255</v>
       </c>
       <c r="T22">
-        <v>1.046559017032865</v>
+        <v>1.059806599526952</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.1292372261706297</v>
+        <v>0.1230830725434568</v>
       </c>
       <c r="W22">
-        <v>0.2053258620689655</v>
+        <v>0.2067770114942529</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.3692492176303704</v>
+        <v>0.3516659215527339</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.2500069213700503</v>
+        <v>0.2519069213700503</v>
       </c>
       <c r="C23">
-        <v>22.94182700982145</v>
+        <v>22.34326933337185</v>
       </c>
       <c r="D23">
-        <v>27.17982700982145</v>
+        <v>26.92926933337185</v>
       </c>
       <c r="E23">
-        <v>7.307999999999999</v>
+        <v>7.656</v>
       </c>
       <c r="F23">
-        <v>7.307999999999999</v>
+        <v>7.656</v>
       </c>
       <c r="G23">
         <v>3.07</v>
@@ -3167,37 +3167,37 @@
         <v>0.606</v>
       </c>
       <c r="M23">
-        <v>1.7232264</v>
+        <v>1.8052848</v>
       </c>
       <c r="N23">
-        <v>-1.1172264</v>
+        <v>-1.1992848</v>
       </c>
       <c r="O23">
-        <v>-0.3910292399999999</v>
+        <v>-0.41974968</v>
       </c>
       <c r="P23">
-        <v>-0.7261971599999999</v>
+        <v>-0.77953512</v>
       </c>
       <c r="Q23">
-        <v>-0.3021971599999999</v>
+        <v>-0.35553512</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2614984164003255</v>
+        <v>0.2642637807131502</v>
       </c>
       <c r="T23">
-        <v>1.059806599526952</v>
+        <v>1.073393863623451</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.1230830725434569</v>
+        <v>0.1174883874278452</v>
       </c>
       <c r="W23">
-        <v>0.2067770114942529</v>
+        <v>0.2080962382445141</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.3516659215527339</v>
+        <v>0.3356811069367005</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.2519069213700503</v>
+        <v>0.2538069213700503</v>
       </c>
       <c r="C24">
-        <v>22.34326933337185</v>
+        <v>21.74928900061946</v>
       </c>
       <c r="D24">
-        <v>26.92926933337185</v>
+        <v>26.68328900061945</v>
       </c>
       <c r="E24">
-        <v>7.656</v>
+        <v>8.004</v>
       </c>
       <c r="F24">
-        <v>7.656</v>
+        <v>8.004</v>
       </c>
       <c r="G24">
         <v>3.07</v>
@@ -3249,37 +3249,37 @@
         <v>0.606</v>
       </c>
       <c r="M24">
-        <v>1.8052848</v>
+        <v>1.8873432</v>
       </c>
       <c r="N24">
-        <v>-1.1992848</v>
+        <v>-1.2813432</v>
       </c>
       <c r="O24">
-        <v>-0.41974968</v>
+        <v>-0.4484701199999999</v>
       </c>
       <c r="P24">
-        <v>-0.77953512</v>
+        <v>-0.8328730799999999</v>
       </c>
       <c r="Q24">
-        <v>-0.35553512</v>
+        <v>-0.4088730799999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2642637807131502</v>
+        <v>0.2671009726704638</v>
       </c>
       <c r="T24">
-        <v>1.073393863623451</v>
+        <v>1.087334043670509</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.1174883874278452</v>
+        <v>0.1123801966701128</v>
       </c>
       <c r="W24">
-        <v>0.2080962382445141</v>
+        <v>0.2093007496251874</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.3356811069367005</v>
+        <v>0.3210862762003223</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.2538069213700503</v>
+        <v>0.2557069213700503</v>
       </c>
       <c r="C25">
-        <v>21.74928900061946</v>
+        <v>21.15976171428571</v>
       </c>
       <c r="D25">
-        <v>26.68328900061945</v>
+        <v>26.44176171428571</v>
       </c>
       <c r="E25">
-        <v>8.004</v>
+        <v>8.352</v>
       </c>
       <c r="F25">
-        <v>8.004</v>
+        <v>8.352</v>
       </c>
       <c r="G25">
         <v>3.07</v>
@@ -3331,37 +3331,37 @@
         <v>0.606</v>
       </c>
       <c r="M25">
-        <v>1.8873432</v>
+        <v>1.9694016</v>
       </c>
       <c r="N25">
-        <v>-1.2813432</v>
+        <v>-1.3634016</v>
       </c>
       <c r="O25">
-        <v>-0.4484701199999999</v>
+        <v>-0.47719056</v>
       </c>
       <c r="P25">
-        <v>-0.8328730799999999</v>
+        <v>-0.8862110400000001</v>
       </c>
       <c r="Q25">
-        <v>-0.4088730799999999</v>
+        <v>-0.46221104</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2671009726704638</v>
+        <v>0.2700128275740226</v>
       </c>
       <c r="T25">
-        <v>1.087334043670509</v>
+        <v>1.101641070560911</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.1123801966701128</v>
+        <v>0.1076976884755247</v>
       </c>
       <c r="W25">
-        <v>0.2093007496251874</v>
+        <v>0.2104048850574713</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.3210862762003223</v>
+        <v>0.3077076813586421</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.2557069213700502</v>
+        <v>0.2576069213700503</v>
       </c>
       <c r="C26">
-        <v>21.15976171428572</v>
+        <v>20.57456763709422</v>
       </c>
       <c r="D26">
-        <v>26.44176171428572</v>
+        <v>26.20456763709421</v>
       </c>
       <c r="E26">
-        <v>8.351999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="F26">
-        <v>8.351999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="G26">
         <v>3.07</v>
@@ -3413,37 +3413,37 @@
         <v>0.606</v>
       </c>
       <c r="M26">
-        <v>1.9694016</v>
+        <v>2.05146</v>
       </c>
       <c r="N26">
-        <v>-1.3634016</v>
+        <v>-1.44546</v>
       </c>
       <c r="O26">
-        <v>-0.4771905599999998</v>
+        <v>-0.505911</v>
       </c>
       <c r="P26">
-        <v>-0.8862110399999997</v>
+        <v>-0.9395490000000002</v>
       </c>
       <c r="Q26">
-        <v>-0.4622110399999997</v>
+        <v>-0.5155490000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2700128275740226</v>
+        <v>0.2730023319416762</v>
       </c>
       <c r="T26">
-        <v>1.101641070560911</v>
+        <v>1.116329618168389</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.1076976884755248</v>
+        <v>0.1033897809365038</v>
       </c>
       <c r="W26">
-        <v>0.2104048850574713</v>
+        <v>0.2114206896551724</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.3077076813586422</v>
+        <v>0.2953993741042964</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.2576069213700503</v>
+        <v>0.2595069213700503</v>
       </c>
       <c r="C27">
-        <v>20.57456763709422</v>
+        <v>19.99359119350834</v>
       </c>
       <c r="D27">
-        <v>26.20456763709421</v>
+        <v>25.97159119350835</v>
       </c>
       <c r="E27">
-        <v>8.699999999999999</v>
+        <v>9.048</v>
       </c>
       <c r="F27">
-        <v>8.699999999999999</v>
+        <v>9.048</v>
       </c>
       <c r="G27">
         <v>3.07</v>
@@ -3495,37 +3495,37 @@
         <v>0.606</v>
       </c>
       <c r="M27">
-        <v>2.05146</v>
+        <v>2.1335184</v>
       </c>
       <c r="N27">
-        <v>-1.44546</v>
+        <v>-1.5275184</v>
       </c>
       <c r="O27">
-        <v>-0.505911</v>
+        <v>-0.5346314400000001</v>
       </c>
       <c r="P27">
-        <v>-0.9395490000000002</v>
+        <v>-0.9928869600000003</v>
       </c>
       <c r="Q27">
-        <v>-0.5155490000000001</v>
+        <v>-0.5688869600000003</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2730023319416762</v>
+        <v>0.2760726337246718</v>
       </c>
       <c r="T27">
-        <v>1.116329618168389</v>
+        <v>1.131415153549043</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1033897809365038</v>
+        <v>0.09941325090048436</v>
       </c>
       <c r="W27">
-        <v>0.2114206896551724</v>
+        <v>0.2123583554376658</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2953993741042964</v>
+        <v>0.2840378597156695</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.2595069213700503</v>
+        <v>0.2614069213700503</v>
       </c>
       <c r="C28">
-        <v>19.99359119350834</v>
+        <v>19.41672088195201</v>
       </c>
       <c r="D28">
-        <v>25.97159119350835</v>
+        <v>25.74272088195201</v>
       </c>
       <c r="E28">
-        <v>9.048</v>
+        <v>9.395999999999999</v>
       </c>
       <c r="F28">
-        <v>9.048</v>
+        <v>9.395999999999999</v>
       </c>
       <c r="G28">
         <v>3.07</v>
@@ -3577,37 +3577,37 @@
         <v>0.606</v>
       </c>
       <c r="M28">
-        <v>2.1335184</v>
+        <v>2.2155768</v>
       </c>
       <c r="N28">
-        <v>-1.5275184</v>
+        <v>-1.6095768</v>
       </c>
       <c r="O28">
-        <v>-0.5346314400000001</v>
+        <v>-0.56335188</v>
       </c>
       <c r="P28">
-        <v>-0.9928869600000003</v>
+        <v>-1.04622492</v>
       </c>
       <c r="Q28">
-        <v>-0.5688869600000003</v>
+        <v>-0.6222249200000002</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2760726337246718</v>
+        <v>0.2792270533647359</v>
       </c>
       <c r="T28">
-        <v>1.131415153549043</v>
+        <v>1.146913991268893</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.09941325090048436</v>
+        <v>0.09573127864491088</v>
       </c>
       <c r="W28">
-        <v>0.2123583554376658</v>
+        <v>0.21322656449553</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2840378597156695</v>
+        <v>0.2735179389854596</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.2614069213700503</v>
+        <v>0.2633069213700503</v>
       </c>
       <c r="C29">
-        <v>19.41672088195201</v>
+        <v>18.84384909687214</v>
       </c>
       <c r="D29">
-        <v>25.74272088195201</v>
+        <v>25.51784909687214</v>
       </c>
       <c r="E29">
-        <v>9.395999999999999</v>
+        <v>9.744</v>
       </c>
       <c r="F29">
-        <v>9.395999999999999</v>
+        <v>9.744</v>
       </c>
       <c r="G29">
         <v>3.07</v>
@@ -3659,37 +3659,37 @@
         <v>0.606</v>
       </c>
       <c r="M29">
-        <v>2.2155768</v>
+        <v>2.2976352</v>
       </c>
       <c r="N29">
-        <v>-1.6095768</v>
+        <v>-1.6916352</v>
       </c>
       <c r="O29">
-        <v>-0.56335188</v>
+        <v>-0.5920723200000001</v>
       </c>
       <c r="P29">
-        <v>-1.04622492</v>
+        <v>-1.09956288</v>
       </c>
       <c r="Q29">
-        <v>-0.6222249200000002</v>
+        <v>-0.6755628800000001</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2792270533647359</v>
+        <v>0.2824690957725794</v>
       </c>
       <c r="T29">
-        <v>1.146913991268893</v>
+        <v>1.162843352258739</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09573127864491088</v>
+        <v>0.09231230440759261</v>
       </c>
       <c r="W29">
-        <v>0.21322656449553</v>
+        <v>0.2140327586206897</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2735179389854596</v>
+        <v>0.2637494411645503</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.2633069213700503</v>
+        <v>0.2652069213700503</v>
       </c>
       <c r="C30">
-        <v>18.84384909687214</v>
+        <v>18.27487196004662</v>
       </c>
       <c r="D30">
-        <v>25.51784909687214</v>
+        <v>25.29687196004662</v>
       </c>
       <c r="E30">
-        <v>9.744</v>
+        <v>10.092</v>
       </c>
       <c r="F30">
-        <v>9.744</v>
+        <v>10.092</v>
       </c>
       <c r="G30">
         <v>3.07</v>
@@ -3741,37 +3741,37 @@
         <v>0.606</v>
       </c>
       <c r="M30">
-        <v>2.2976352</v>
+        <v>2.3796936</v>
       </c>
       <c r="N30">
-        <v>-1.6916352</v>
+        <v>-1.773693600000001</v>
       </c>
       <c r="O30">
-        <v>-0.5920723200000001</v>
+        <v>-0.6207927600000002</v>
       </c>
       <c r="P30">
-        <v>-1.09956288</v>
+        <v>-1.15290084</v>
       </c>
       <c r="Q30">
-        <v>-0.6755628800000001</v>
+        <v>-0.7289008400000004</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2824690957725794</v>
+        <v>0.285802463318672</v>
       </c>
       <c r="T30">
-        <v>1.162843352258739</v>
+        <v>1.179221427642665</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.09231230440759261</v>
+        <v>0.08912912149698597</v>
       </c>
       <c r="W30">
-        <v>0.2140327586206897</v>
+        <v>0.2147833531510107</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.2637494411645503</v>
+        <v>0.2546546328485313</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.2652069213700503</v>
+        <v>0.2671069213700503</v>
       </c>
       <c r="C31">
-        <v>18.27487196004662</v>
+        <v>17.7096891605818</v>
       </c>
       <c r="D31">
-        <v>25.29687196004662</v>
+        <v>25.0796891605818</v>
       </c>
       <c r="E31">
-        <v>10.092</v>
+        <v>10.44</v>
       </c>
       <c r="F31">
-        <v>10.092</v>
+        <v>10.44</v>
       </c>
       <c r="G31">
         <v>3.07</v>
@@ -3823,37 +3823,37 @@
         <v>0.606</v>
       </c>
       <c r="M31">
-        <v>2.3796936</v>
+        <v>2.461752</v>
       </c>
       <c r="N31">
-        <v>-1.7736936</v>
+        <v>-1.855752</v>
       </c>
       <c r="O31">
-        <v>-0.6207927599999999</v>
+        <v>-0.6495132</v>
       </c>
       <c r="P31">
-        <v>-1.15290084</v>
+        <v>-1.2062388</v>
       </c>
       <c r="Q31">
-        <v>-0.72890084</v>
+        <v>-0.7822388000000003</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.285802463318672</v>
+        <v>0.2892310699375102</v>
       </c>
       <c r="T31">
-        <v>1.179221427642665</v>
+        <v>1.19606744803756</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08912912149698599</v>
+        <v>0.08615815078041979</v>
       </c>
       <c r="W31">
-        <v>0.2147833531510107</v>
+        <v>0.215483908045977</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.2546546328485314</v>
+        <v>0.2461661450869136</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.2671069213700503</v>
+        <v>0.2690069213700503</v>
       </c>
       <c r="C32">
-        <v>17.7096891605818</v>
+        <v>17.14820380308203</v>
       </c>
       <c r="D32">
-        <v>25.0796891605818</v>
+        <v>24.86620380308203</v>
       </c>
       <c r="E32">
-        <v>10.44</v>
+        <v>10.788</v>
       </c>
       <c r="F32">
-        <v>10.44</v>
+        <v>10.788</v>
       </c>
       <c r="G32">
         <v>3.07</v>
@@ -3905,37 +3905,37 @@
         <v>0.606</v>
       </c>
       <c r="M32">
-        <v>2.461752</v>
+        <v>2.5438104</v>
       </c>
       <c r="N32">
-        <v>-1.855752</v>
+        <v>-1.9378104</v>
       </c>
       <c r="O32">
-        <v>-0.6495132</v>
+        <v>-0.67823364</v>
       </c>
       <c r="P32">
-        <v>-1.2062388</v>
+        <v>-1.25957676</v>
       </c>
       <c r="Q32">
-        <v>-0.7822388000000003</v>
+        <v>-0.83557676</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2892310699375102</v>
+        <v>0.2927590564583438</v>
       </c>
       <c r="T32">
-        <v>1.19606744803756</v>
+        <v>1.213401758878684</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08615815078041979</v>
+        <v>0.08337885559395464</v>
       </c>
       <c r="W32">
-        <v>0.215483908045977</v>
+        <v>0.2161392658509455</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.2461661450869136</v>
+        <v>0.2382253016970133</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.2690069213700503</v>
+        <v>0.2709069213700502</v>
       </c>
       <c r="C33">
-        <v>17.14820380308203</v>
+        <v>16.59032226350828</v>
       </c>
       <c r="D33">
-        <v>24.86620380308203</v>
+        <v>24.65632226350828</v>
       </c>
       <c r="E33">
-        <v>10.788</v>
+        <v>11.136</v>
       </c>
       <c r="F33">
-        <v>10.788</v>
+        <v>11.136</v>
       </c>
       <c r="G33">
         <v>3.07</v>
@@ -3987,37 +3987,37 @@
         <v>0.606</v>
       </c>
       <c r="M33">
-        <v>2.5438104</v>
+        <v>2.6258688</v>
       </c>
       <c r="N33">
-        <v>-1.9378104</v>
+        <v>-2.0198688</v>
       </c>
       <c r="O33">
-        <v>-0.67823364</v>
+        <v>-0.70695408</v>
       </c>
       <c r="P33">
-        <v>-1.25957676</v>
+        <v>-1.31291472</v>
       </c>
       <c r="Q33">
-        <v>-0.83557676</v>
+        <v>-0.8889147200000002</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2927590564583438</v>
+        <v>0.2963908072886135</v>
       </c>
       <c r="T33">
-        <v>1.213401758878684</v>
+        <v>1.231245902391606</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08337885559395464</v>
+        <v>0.08077326635664356</v>
       </c>
       <c r="W33">
-        <v>0.2161392658509455</v>
+        <v>0.2167536637931035</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.2382253016970133</v>
+        <v>0.2307807610189816</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.2709069213700502</v>
+        <v>0.2728069213700502</v>
       </c>
       <c r="C34">
-        <v>16.59032226350828</v>
+        <v>16.0359540522752</v>
       </c>
       <c r="D34">
-        <v>24.65632226350828</v>
+        <v>24.4499540522752</v>
       </c>
       <c r="E34">
-        <v>11.136</v>
+        <v>11.484</v>
       </c>
       <c r="F34">
-        <v>11.136</v>
+        <v>11.484</v>
       </c>
       <c r="G34">
         <v>3.07</v>
@@ -4069,37 +4069,37 @@
         <v>0.606</v>
       </c>
       <c r="M34">
-        <v>2.6258688</v>
+        <v>2.7079272</v>
       </c>
       <c r="N34">
-        <v>-2.0198688</v>
+        <v>-2.1019272</v>
       </c>
       <c r="O34">
-        <v>-0.70695408</v>
+        <v>-0.7356745200000001</v>
       </c>
       <c r="P34">
-        <v>-1.31291472</v>
+        <v>-1.36625268</v>
       </c>
       <c r="Q34">
-        <v>-0.8889147200000002</v>
+        <v>-0.9422526800000003</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2963908072886135</v>
+        <v>0.3001309685914286</v>
       </c>
       <c r="T34">
-        <v>1.231245902391606</v>
+        <v>1.249622706904914</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08077326635664356</v>
+        <v>0.07832559161856344</v>
       </c>
       <c r="W34">
-        <v>0.2167536637931035</v>
+        <v>0.2173308254963427</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.2307807610189816</v>
+        <v>0.2237874046244669</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.2728069213700502</v>
+        <v>0.2747069213700503</v>
       </c>
       <c r="C35">
-        <v>16.0359540522752</v>
+        <v>15.48501168416644</v>
       </c>
       <c r="D35">
-        <v>24.4499540522752</v>
+        <v>24.24701168416644</v>
       </c>
       <c r="E35">
-        <v>11.484</v>
+        <v>11.832</v>
       </c>
       <c r="F35">
-        <v>11.484</v>
+        <v>11.832</v>
       </c>
       <c r="G35">
         <v>3.07</v>
@@ -4151,37 +4151,37 @@
         <v>0.606</v>
       </c>
       <c r="M35">
-        <v>2.7079272</v>
+        <v>2.789985600000001</v>
       </c>
       <c r="N35">
-        <v>-2.1019272</v>
+        <v>-2.183985600000001</v>
       </c>
       <c r="O35">
-        <v>-0.7356745200000001</v>
+        <v>-0.7643949600000002</v>
       </c>
       <c r="P35">
-        <v>-1.36625268</v>
+        <v>-1.41959064</v>
       </c>
       <c r="Q35">
-        <v>-0.9422526800000003</v>
+        <v>-0.9955906400000004</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.3001309685914286</v>
+        <v>0.3039844681155412</v>
       </c>
       <c r="T35">
-        <v>1.249622706904914</v>
+        <v>1.268556384282261</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07832559161856344</v>
+        <v>0.07602189774742922</v>
       </c>
       <c r="W35">
-        <v>0.2173308254963427</v>
+        <v>0.2178740365111562</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.2237874046244669</v>
+        <v>0.217205422135512</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.2747069213700503</v>
+        <v>0.2766069213700503</v>
       </c>
       <c r="C36">
-        <v>15.48501168416644</v>
+        <v>14.93741055467495</v>
       </c>
       <c r="D36">
-        <v>24.24701168416644</v>
+        <v>24.04741055467495</v>
       </c>
       <c r="E36">
-        <v>11.832</v>
+        <v>12.18</v>
       </c>
       <c r="F36">
-        <v>11.832</v>
+        <v>12.18</v>
       </c>
       <c r="G36">
         <v>3.07</v>
@@ -4233,37 +4233,37 @@
         <v>0.606</v>
       </c>
       <c r="M36">
-        <v>2.789985600000001</v>
+        <v>2.872044</v>
       </c>
       <c r="N36">
-        <v>-2.183985600000001</v>
+        <v>-2.266044</v>
       </c>
       <c r="O36">
-        <v>-0.7643949600000002</v>
+        <v>-0.7931154000000001</v>
       </c>
       <c r="P36">
-        <v>-1.41959064</v>
+        <v>-1.4729286</v>
       </c>
       <c r="Q36">
-        <v>-0.9955906400000004</v>
+        <v>-1.0489286</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.3039844681155412</v>
+        <v>0.3079565368557803</v>
       </c>
       <c r="T36">
-        <v>1.268556384282261</v>
+        <v>1.288072636348142</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07602189774742922</v>
+        <v>0.0738498435260741</v>
       </c>
       <c r="W36">
-        <v>0.2178740365111562</v>
+        <v>0.2183862068965517</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.217205422135512</v>
+        <v>0.2109995529316403</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.2766069213700503</v>
+        <v>0.2785069213700503</v>
       </c>
       <c r="C37">
-        <v>14.93741055467495</v>
+        <v>14.39306882240122</v>
       </c>
       <c r="D37">
-        <v>24.04741055467495</v>
+        <v>23.85106882240122</v>
       </c>
       <c r="E37">
-        <v>12.18</v>
+        <v>12.528</v>
       </c>
       <c r="F37">
-        <v>12.18</v>
+        <v>12.528</v>
       </c>
       <c r="G37">
         <v>3.07</v>
@@ -4315,37 +4315,37 @@
         <v>0.606</v>
       </c>
       <c r="M37">
-        <v>2.872044</v>
+        <v>2.9541024</v>
       </c>
       <c r="N37">
-        <v>-2.266044</v>
+        <v>-2.3481024</v>
       </c>
       <c r="O37">
-        <v>-0.7931154000000001</v>
+        <v>-0.82183584</v>
       </c>
       <c r="P37">
-        <v>-1.4729286</v>
+        <v>-1.52626656</v>
       </c>
       <c r="Q37">
-        <v>-1.0489286</v>
+        <v>-1.10226656</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.3079565368557803</v>
+        <v>0.3120527327441519</v>
       </c>
       <c r="T37">
-        <v>1.288072636348142</v>
+        <v>1.308198771291082</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0738498435260741</v>
+        <v>0.07179845898368316</v>
       </c>
       <c r="W37">
-        <v>0.2183862068965517</v>
+        <v>0.2188699233716475</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.2109995529316403</v>
+        <v>0.2051384542390947</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.2785069213700503</v>
+        <v>0.2804069213700503</v>
       </c>
       <c r="C38">
-        <v>14.39306882240122</v>
+        <v>13.85190729716607</v>
       </c>
       <c r="D38">
-        <v>23.85106882240122</v>
+        <v>23.65790729716607</v>
       </c>
       <c r="E38">
-        <v>12.528</v>
+        <v>12.876</v>
       </c>
       <c r="F38">
-        <v>12.528</v>
+        <v>12.876</v>
       </c>
       <c r="G38">
         <v>3.07</v>
@@ -4397,37 +4397,37 @@
         <v>0.606</v>
       </c>
       <c r="M38">
-        <v>2.9541024</v>
+        <v>3.0361608</v>
       </c>
       <c r="N38">
-        <v>-2.3481024</v>
+        <v>-2.4301608</v>
       </c>
       <c r="O38">
-        <v>-0.82183584</v>
+        <v>-0.8505562799999999</v>
       </c>
       <c r="P38">
-        <v>-1.52626656</v>
+        <v>-1.57960452</v>
       </c>
       <c r="Q38">
-        <v>-1.10226656</v>
+        <v>-1.15560452</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.3120527327441519</v>
+        <v>0.3162789665972336</v>
       </c>
       <c r="T38">
-        <v>1.308198771291081</v>
+        <v>1.328963831152844</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07179845898368316</v>
+        <v>0.06985796009223226</v>
       </c>
       <c r="W38">
-        <v>0.2188699233716475</v>
+        <v>0.2193274930102516</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2051384542390947</v>
+        <v>0.1995941716920921</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.2804069213700503</v>
+        <v>0.2823069213700503</v>
       </c>
       <c r="C39">
-        <v>13.85190729716607</v>
+        <v>13.31384933351652</v>
       </c>
       <c r="D39">
-        <v>23.65790729716607</v>
+        <v>23.46784933351652</v>
       </c>
       <c r="E39">
-        <v>12.876</v>
+        <v>13.224</v>
       </c>
       <c r="F39">
-        <v>12.876</v>
+        <v>13.224</v>
       </c>
       <c r="G39">
         <v>3.07</v>
@@ -4479,37 +4479,37 @@
         <v>0.606</v>
       </c>
       <c r="M39">
-        <v>3.0361608</v>
+        <v>3.1182192</v>
       </c>
       <c r="N39">
-        <v>-2.4301608</v>
+        <v>-2.5122192</v>
       </c>
       <c r="O39">
-        <v>-0.8505562799999999</v>
+        <v>-0.87927672</v>
       </c>
       <c r="P39">
-        <v>-1.57960452</v>
+        <v>-1.63294248</v>
       </c>
       <c r="Q39">
-        <v>-1.15560452</v>
+        <v>-1.20894248</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.3162789665972336</v>
+        <v>0.3206415305746083</v>
       </c>
       <c r="T39">
-        <v>1.328963831152844</v>
+        <v>1.35039873165531</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06985796009223226</v>
+        <v>0.06801959272138404</v>
       </c>
       <c r="W39">
-        <v>0.2193274930102516</v>
+        <v>0.2197609800362977</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1995941716920921</v>
+        <v>0.1943416934896687</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.2823069213700503</v>
+        <v>0.2842069213700503</v>
       </c>
       <c r="C40">
-        <v>13.31384933351652</v>
+        <v>12.77882072932397</v>
       </c>
       <c r="D40">
-        <v>23.46784933351652</v>
+        <v>23.28082072932397</v>
       </c>
       <c r="E40">
-        <v>13.224</v>
+        <v>13.572</v>
       </c>
       <c r="F40">
-        <v>13.224</v>
+        <v>13.572</v>
       </c>
       <c r="G40">
         <v>3.07</v>
@@ -4561,37 +4561,37 @@
         <v>0.606</v>
       </c>
       <c r="M40">
-        <v>3.1182192</v>
+        <v>3.2002776</v>
       </c>
       <c r="N40">
-        <v>-2.5122192</v>
+        <v>-2.5942776</v>
       </c>
       <c r="O40">
-        <v>-0.87927672</v>
+        <v>-0.9079971599999999</v>
       </c>
       <c r="P40">
-        <v>-1.63294248</v>
+        <v>-1.68628044</v>
       </c>
       <c r="Q40">
-        <v>-1.20894248</v>
+        <v>-1.26228044</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.3206415305746083</v>
+        <v>0.3251471294364872</v>
       </c>
       <c r="T40">
-        <v>1.35039873165531</v>
+        <v>1.372536415780807</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06801959272138404</v>
+        <v>0.06627550060032292</v>
       </c>
       <c r="W40">
-        <v>0.2197609800362977</v>
+        <v>0.2201722369584438</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1943416934896687</v>
+        <v>0.1893585731437798</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.2842069213700503</v>
+        <v>0.2861069213700503</v>
       </c>
       <c r="C41">
-        <v>12.77882072932397</v>
+        <v>12.24674962919283</v>
       </c>
       <c r="D41">
-        <v>23.28082072932397</v>
+        <v>23.09674962919282</v>
       </c>
       <c r="E41">
-        <v>13.572</v>
+        <v>13.92</v>
       </c>
       <c r="F41">
-        <v>13.572</v>
+        <v>13.92</v>
       </c>
       <c r="G41">
         <v>3.07</v>
@@ -4643,37 +4643,37 @@
         <v>0.606</v>
       </c>
       <c r="M41">
-        <v>3.2002776</v>
+        <v>3.282336</v>
       </c>
       <c r="N41">
-        <v>-2.5942776</v>
+        <v>-2.676336</v>
       </c>
       <c r="O41">
-        <v>-0.9079971599999999</v>
+        <v>-0.9367175999999999</v>
       </c>
       <c r="P41">
-        <v>-1.68628044</v>
+        <v>-1.7396184</v>
       </c>
       <c r="Q41">
-        <v>-1.26228044</v>
+        <v>-1.3156184</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.3251471294364872</v>
+        <v>0.3298029149270953</v>
       </c>
       <c r="T41">
-        <v>1.372536415780807</v>
+        <v>1.395412022710487</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06627550060032292</v>
+        <v>0.06461861308531484</v>
       </c>
       <c r="W41">
-        <v>0.2201722369584438</v>
+        <v>0.2205629310344828</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1893585731437798</v>
+        <v>0.1846246088151853</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.2861069213700503</v>
+        <v>0.2880069213700503</v>
       </c>
       <c r="C42">
-        <v>12.24674962919283</v>
+        <v>11.71756643241531</v>
       </c>
       <c r="D42">
-        <v>23.09674962919282</v>
+        <v>22.91556643241531</v>
       </c>
       <c r="E42">
-        <v>13.92</v>
+        <v>14.268</v>
       </c>
       <c r="F42">
-        <v>13.92</v>
+        <v>14.268</v>
       </c>
       <c r="G42">
         <v>3.07</v>
@@ -4725,37 +4725,37 @@
         <v>0.606</v>
       </c>
       <c r="M42">
-        <v>3.282336</v>
+        <v>3.3643944</v>
       </c>
       <c r="N42">
-        <v>-2.676336</v>
+        <v>-2.7583944</v>
       </c>
       <c r="O42">
-        <v>-0.9367175999999999</v>
+        <v>-0.96543804</v>
       </c>
       <c r="P42">
-        <v>-1.7396184</v>
+        <v>-1.79295636</v>
       </c>
       <c r="Q42">
-        <v>-1.3156184</v>
+        <v>-1.36895636</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.3298029149270953</v>
+        <v>0.3346165236546732</v>
       </c>
       <c r="T42">
-        <v>1.395412022710487</v>
+        <v>1.419063073942868</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.06461861308531484</v>
+        <v>0.06304254935152667</v>
       </c>
       <c r="W42">
-        <v>0.2205629310344828</v>
+        <v>0.22093456686291</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1846246088151853</v>
+        <v>0.1801215695757905</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.2880069213700503</v>
+        <v>0.2899069213700503</v>
       </c>
       <c r="C43">
-        <v>11.71756643241531</v>
+        <v>11.19120370522501</v>
       </c>
       <c r="D43">
-        <v>22.91556643241531</v>
+        <v>22.73720370522501</v>
       </c>
       <c r="E43">
-        <v>14.268</v>
+        <v>14.616</v>
       </c>
       <c r="F43">
-        <v>14.268</v>
+        <v>14.616</v>
       </c>
       <c r="G43">
         <v>3.07</v>
@@ -4807,37 +4807,37 @@
         <v>0.606</v>
       </c>
       <c r="M43">
-        <v>3.3643944</v>
+        <v>3.4464528</v>
       </c>
       <c r="N43">
-        <v>-2.7583944</v>
+        <v>-2.8404528</v>
       </c>
       <c r="O43">
-        <v>-0.96543804</v>
+        <v>-0.99415848</v>
       </c>
       <c r="P43">
-        <v>-1.79295636</v>
+        <v>-1.84629432</v>
       </c>
       <c r="Q43">
-        <v>-1.36895636</v>
+        <v>-1.42229432</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.3346165236546732</v>
+        <v>0.3395961188900986</v>
       </c>
       <c r="T43">
-        <v>1.419063073942868</v>
+        <v>1.443529678666021</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06304254935152667</v>
+        <v>0.06154153627172842</v>
       </c>
       <c r="W43">
-        <v>0.22093456686291</v>
+        <v>0.2212885057471264</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1801215695757905</v>
+        <v>0.1758329607763669</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.2899069213700503</v>
+        <v>0.2918069213700503</v>
       </c>
       <c r="C44">
-        <v>11.19120370522502</v>
+        <v>10.66759609711653</v>
       </c>
       <c r="D44">
-        <v>22.73720370522501</v>
+        <v>22.56159609711653</v>
       </c>
       <c r="E44">
-        <v>14.616</v>
+        <v>14.964</v>
       </c>
       <c r="F44">
-        <v>14.616</v>
+        <v>14.964</v>
       </c>
       <c r="G44">
         <v>3.07</v>
@@ -4889,37 +4889,37 @@
         <v>0.606</v>
       </c>
       <c r="M44">
-        <v>3.446452799999999</v>
+        <v>3.5285112</v>
       </c>
       <c r="N44">
-        <v>-2.8404528</v>
+        <v>-2.9225112</v>
       </c>
       <c r="O44">
-        <v>-0.9941584799999997</v>
+        <v>-1.02287892</v>
       </c>
       <c r="P44">
-        <v>-1.84629432</v>
+        <v>-1.89963228</v>
       </c>
       <c r="Q44">
-        <v>-1.42229432</v>
+        <v>-1.47563228</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.3395961188900986</v>
+        <v>0.3447504367653634</v>
       </c>
       <c r="T44">
-        <v>1.443529678666021</v>
+        <v>1.468854760747881</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06154153627172843</v>
+        <v>0.06011033775378125</v>
       </c>
       <c r="W44">
-        <v>0.2212885057471264</v>
+        <v>0.2216259823576584</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1758329607763669</v>
+        <v>0.1717438221536607</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.2918069213700503</v>
+        <v>0.2937069213700503</v>
       </c>
       <c r="C45">
-        <v>10.66759609711653</v>
+        <v>10.14668026101312</v>
       </c>
       <c r="D45">
-        <v>22.56159609711653</v>
+        <v>22.38868026101312</v>
       </c>
       <c r="E45">
-        <v>14.964</v>
+        <v>15.312</v>
       </c>
       <c r="F45">
-        <v>14.964</v>
+        <v>15.312</v>
       </c>
       <c r="G45">
         <v>3.07</v>
@@ -4971,37 +4971,37 @@
         <v>0.606</v>
       </c>
       <c r="M45">
-        <v>3.5285112</v>
+        <v>3.6105696</v>
       </c>
       <c r="N45">
-        <v>-2.9225112</v>
+        <v>-3.0045696</v>
       </c>
       <c r="O45">
-        <v>-1.02287892</v>
+        <v>-1.05159936</v>
       </c>
       <c r="P45">
-        <v>-1.89963228</v>
+        <v>-1.95297024</v>
       </c>
       <c r="Q45">
-        <v>-1.47563228</v>
+        <v>-1.52897024</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.3447504367653634</v>
+        <v>0.3500888374218878</v>
       </c>
       <c r="T45">
-        <v>1.468854760747881</v>
+        <v>1.49508431004695</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06011033775378125</v>
+        <v>0.05874419371392258</v>
       </c>
       <c r="W45">
-        <v>0.2216259823576584</v>
+        <v>0.2219481191222571</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1717438221536607</v>
+        <v>0.1678405534683503</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.2937069213700503</v>
+        <v>0.2956069213700503</v>
       </c>
       <c r="C46">
-        <v>10.14668026101312</v>
+        <v>9.628394777077668</v>
       </c>
       <c r="D46">
-        <v>22.38868026101312</v>
+        <v>22.21839477707767</v>
       </c>
       <c r="E46">
-        <v>15.312</v>
+        <v>15.66</v>
       </c>
       <c r="F46">
-        <v>15.312</v>
+        <v>15.66</v>
       </c>
       <c r="G46">
         <v>3.07</v>
@@ -5053,37 +5053,37 @@
         <v>0.606</v>
       </c>
       <c r="M46">
-        <v>3.6105696</v>
+        <v>3.692628</v>
       </c>
       <c r="N46">
-        <v>-3.0045696</v>
+        <v>-3.086628</v>
       </c>
       <c r="O46">
-        <v>-1.05159936</v>
+        <v>-1.0803198</v>
       </c>
       <c r="P46">
-        <v>-1.95297024</v>
+        <v>-2.0063082</v>
       </c>
       <c r="Q46">
-        <v>-1.52897024</v>
+        <v>-1.5823082</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.3500888374218878</v>
+        <v>0.3556213617386494</v>
       </c>
       <c r="T46">
-        <v>1.49508431004695</v>
+        <v>1.522267661138713</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05874419371392258</v>
+        <v>0.05743876718694653</v>
       </c>
       <c r="W46">
-        <v>0.2219481191222571</v>
+        <v>0.222255938697318</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1678405534683503</v>
+        <v>0.1641107633912758</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.2956069213700503</v>
+        <v>0.2975069213700503</v>
       </c>
       <c r="C47">
-        <v>9.628394777077668</v>
+        <v>9.112680079974108</v>
       </c>
       <c r="D47">
-        <v>22.21839477707767</v>
+        <v>22.05068007997411</v>
       </c>
       <c r="E47">
-        <v>15.66</v>
+        <v>16.008</v>
       </c>
       <c r="F47">
-        <v>15.66</v>
+        <v>16.008</v>
       </c>
       <c r="G47">
         <v>3.07</v>
@@ -5135,37 +5135,37 @@
         <v>0.606</v>
       </c>
       <c r="M47">
-        <v>3.692628</v>
+        <v>3.7746864</v>
       </c>
       <c r="N47">
-        <v>-3.086628</v>
+        <v>-3.1686864</v>
       </c>
       <c r="O47">
-        <v>-1.0803198</v>
+        <v>-1.10904024</v>
       </c>
       <c r="P47">
-        <v>-2.0063082</v>
+        <v>-2.05964616</v>
       </c>
       <c r="Q47">
-        <v>-1.5823082</v>
+        <v>-1.63564616</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.3556213617386494</v>
+        <v>0.3613587943634392</v>
       </c>
       <c r="T47">
-        <v>1.522267661138713</v>
+        <v>1.550457803011652</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05743876718694653</v>
+        <v>0.05619009833505639</v>
       </c>
       <c r="W47">
-        <v>0.222255938697318</v>
+        <v>0.2225503748125937</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1641107633912758</v>
+        <v>0.1605431381001611</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.2975069213700503</v>
+        <v>0.2994069213700503</v>
       </c>
       <c r="C48">
-        <v>9.112680079974108</v>
+        <v>8.59947838939873</v>
       </c>
       <c r="D48">
-        <v>22.05068007997411</v>
+        <v>21.88547838939873</v>
       </c>
       <c r="E48">
-        <v>16.008</v>
+        <v>16.356</v>
       </c>
       <c r="F48">
-        <v>16.008</v>
+        <v>16.356</v>
       </c>
       <c r="G48">
         <v>3.07</v>
@@ -5217,37 +5217,37 @@
         <v>0.606</v>
       </c>
       <c r="M48">
-        <v>3.7746864</v>
+        <v>3.8567448</v>
       </c>
       <c r="N48">
-        <v>-3.1686864</v>
+        <v>-3.2507448</v>
       </c>
       <c r="O48">
-        <v>-1.10904024</v>
+        <v>-1.13776068</v>
       </c>
       <c r="P48">
-        <v>-2.05964616</v>
+        <v>-2.11298412</v>
       </c>
       <c r="Q48">
-        <v>-1.63564616</v>
+        <v>-1.68898412</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.3613587943634392</v>
+        <v>0.3673127338797305</v>
       </c>
       <c r="T48">
-        <v>1.550457803011652</v>
+        <v>1.579711723823193</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05619009833505639</v>
+        <v>0.05499456432792754</v>
       </c>
       <c r="W48">
-        <v>0.2225503748125937</v>
+        <v>0.2228322817314747</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1605431381001611</v>
+        <v>0.1571273266512215</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.2994069213700503</v>
+        <v>0.3013069213700503</v>
       </c>
       <c r="C49">
-        <v>8.59947838939873</v>
+        <v>8.08873364371086</v>
       </c>
       <c r="D49">
-        <v>21.88547838939873</v>
+        <v>21.72273364371086</v>
       </c>
       <c r="E49">
-        <v>16.356</v>
+        <v>16.704</v>
       </c>
       <c r="F49">
-        <v>16.356</v>
+        <v>16.704</v>
       </c>
       <c r="G49">
         <v>3.07</v>
@@ -5299,37 +5299,37 @@
         <v>0.606</v>
       </c>
       <c r="M49">
-        <v>3.8567448</v>
+        <v>3.9388032</v>
       </c>
       <c r="N49">
-        <v>-3.2507448</v>
+        <v>-3.3328032</v>
       </c>
       <c r="O49">
-        <v>-1.13776068</v>
+        <v>-1.16648112</v>
       </c>
       <c r="P49">
-        <v>-2.11298412</v>
+        <v>-2.16632208</v>
       </c>
       <c r="Q49">
-        <v>-1.68898412</v>
+        <v>-1.742322080000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.3673127338797305</v>
+        <v>0.3734956710697254</v>
       </c>
       <c r="T49">
-        <v>1.579711723823193</v>
+        <v>1.610090795435177</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05499456432792754</v>
+        <v>0.05384884423776237</v>
       </c>
       <c r="W49">
-        <v>0.2228322817314747</v>
+        <v>0.2231024425287357</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1571273266512215</v>
+        <v>0.1538538406793211</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.3013069213700503</v>
+        <v>0.3032069213700503</v>
       </c>
       <c r="C50">
-        <v>8.088733643710867</v>
+        <v>7.580391436503017</v>
       </c>
       <c r="D50">
-        <v>21.72273364371086</v>
+        <v>21.56239143650302</v>
       </c>
       <c r="E50">
-        <v>16.704</v>
+        <v>17.052</v>
       </c>
       <c r="F50">
-        <v>16.704</v>
+        <v>17.052</v>
       </c>
       <c r="G50">
         <v>3.07</v>
@@ -5381,37 +5381,37 @@
         <v>0.606</v>
       </c>
       <c r="M50">
-        <v>3.938803199999999</v>
+        <v>4.0208616</v>
       </c>
       <c r="N50">
-        <v>-3.332803199999999</v>
+        <v>-3.4148616</v>
       </c>
       <c r="O50">
-        <v>-1.16648112</v>
+        <v>-1.19520156</v>
       </c>
       <c r="P50">
-        <v>-2.16632208</v>
+        <v>-2.21966004</v>
       </c>
       <c r="Q50">
-        <v>-1.74232208</v>
+        <v>-1.79566004</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.3734956710697253</v>
+        <v>0.379921076384818</v>
       </c>
       <c r="T50">
-        <v>1.610090795435177</v>
+        <v>1.641661203188808</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05384884423776238</v>
+        <v>0.05274988823291007</v>
       </c>
       <c r="W50">
-        <v>0.2231024425287357</v>
+        <v>0.2233615763546798</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1538538406793211</v>
+        <v>0.1507139663797431</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.3032069213700503</v>
+        <v>0.3051069213700503</v>
       </c>
       <c r="C51">
-        <v>7.580391436503017</v>
+        <v>7.074398955959506</v>
       </c>
       <c r="D51">
-        <v>21.56239143650302</v>
+        <v>21.4043989559595</v>
       </c>
       <c r="E51">
-        <v>17.052</v>
+        <v>17.4</v>
       </c>
       <c r="F51">
-        <v>17.052</v>
+        <v>17.4</v>
       </c>
       <c r="G51">
         <v>3.07</v>
@@ -5463,37 +5463,37 @@
         <v>0.606</v>
       </c>
       <c r="M51">
-        <v>4.0208616</v>
+        <v>4.10292</v>
       </c>
       <c r="N51">
-        <v>-3.4148616</v>
+        <v>-3.49692</v>
       </c>
       <c r="O51">
-        <v>-1.19520156</v>
+        <v>-1.223922</v>
       </c>
       <c r="P51">
-        <v>-2.21966004</v>
+        <v>-2.272998</v>
       </c>
       <c r="Q51">
-        <v>-1.79566004</v>
+        <v>-1.848998</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.379921076384818</v>
+        <v>0.3866034979125144</v>
       </c>
       <c r="T51">
-        <v>1.641661203188808</v>
+        <v>1.674494427252584</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05274988823291007</v>
+        <v>0.05169489046825188</v>
       </c>
       <c r="W51">
-        <v>0.2233615763546798</v>
+        <v>0.2236103448275862</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1507139663797431</v>
+        <v>0.1476996870521482</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.3051069213700503</v>
+        <v>0.3070069213700503</v>
       </c>
       <c r="C52">
-        <v>7.074398955959506</v>
+        <v>6.570704926861758</v>
       </c>
       <c r="D52">
-        <v>21.4043989559595</v>
+        <v>21.24870492686176</v>
       </c>
       <c r="E52">
-        <v>17.4</v>
+        <v>17.748</v>
       </c>
       <c r="F52">
-        <v>17.4</v>
+        <v>17.748</v>
       </c>
       <c r="G52">
         <v>3.07</v>
@@ -5545,37 +5545,37 @@
         <v>0.606</v>
       </c>
       <c r="M52">
-        <v>4.10292</v>
+        <v>4.184978399999999</v>
       </c>
       <c r="N52">
-        <v>-3.49692</v>
+        <v>-3.5789784</v>
       </c>
       <c r="O52">
-        <v>-1.223922</v>
+        <v>-1.25264244</v>
       </c>
       <c r="P52">
-        <v>-2.272998</v>
+        <v>-2.32633596</v>
       </c>
       <c r="Q52">
-        <v>-1.848998</v>
+        <v>-1.90233596</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.3866034979125144</v>
+        <v>0.3935586713393003</v>
       </c>
       <c r="T52">
-        <v>1.674494427252584</v>
+        <v>1.7086677829108</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.05169489046825188</v>
+        <v>0.05068126516495283</v>
       </c>
       <c r="W52">
-        <v>0.2236103448275862</v>
+        <v>0.2238493576741041</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1476996870521482</v>
+        <v>0.1448036147570081</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.3070069213700503</v>
+        <v>0.3089069213700503</v>
       </c>
       <c r="C53">
-        <v>6.570704926861758</v>
+        <v>6.069259555106385</v>
       </c>
       <c r="D53">
-        <v>21.24870492686176</v>
+        <v>21.09525955510638</v>
       </c>
       <c r="E53">
-        <v>17.748</v>
+        <v>18.096</v>
       </c>
       <c r="F53">
-        <v>17.748</v>
+        <v>18.096</v>
       </c>
       <c r="G53">
         <v>3.07</v>
@@ -5627,37 +5627,37 @@
         <v>0.606</v>
       </c>
       <c r="M53">
-        <v>4.184978399999999</v>
+        <v>4.267036800000001</v>
       </c>
       <c r="N53">
-        <v>-3.5789784</v>
+        <v>-3.661036800000001</v>
       </c>
       <c r="O53">
-        <v>-1.25264244</v>
+        <v>-1.28136288</v>
       </c>
       <c r="P53">
-        <v>-2.32633596</v>
+        <v>-2.379673920000001</v>
       </c>
       <c r="Q53">
-        <v>-1.90233596</v>
+        <v>-1.955673920000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.3935586713393003</v>
+        <v>0.4008036436588692</v>
       </c>
       <c r="T53">
-        <v>1.7086677829108</v>
+        <v>1.744265028388109</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05068126516495283</v>
+        <v>0.04970662545024218</v>
       </c>
       <c r="W53">
-        <v>0.2238493576741041</v>
+        <v>0.2240791777188329</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1448036147570081</v>
+        <v>0.1420189298578348</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.3089069213700503</v>
+        <v>0.3108069213700503</v>
       </c>
       <c r="C54">
-        <v>6.069259555106385</v>
+        <v>5.570014474610034</v>
       </c>
       <c r="D54">
-        <v>21.09525955510638</v>
+        <v>20.94401447461003</v>
       </c>
       <c r="E54">
-        <v>18.096</v>
+        <v>18.444</v>
       </c>
       <c r="F54">
-        <v>18.096</v>
+        <v>18.444</v>
       </c>
       <c r="G54">
         <v>3.07</v>
@@ -5709,37 +5709,37 @@
         <v>0.606</v>
       </c>
       <c r="M54">
-        <v>4.267036800000001</v>
+        <v>4.3490952</v>
       </c>
       <c r="N54">
-        <v>-3.661036800000001</v>
+        <v>-3.7430952</v>
       </c>
       <c r="O54">
-        <v>-1.28136288</v>
+        <v>-1.31008332</v>
       </c>
       <c r="P54">
-        <v>-2.379673920000001</v>
+        <v>-2.43301188</v>
       </c>
       <c r="Q54">
-        <v>-1.955673920000001</v>
+        <v>-2.00901188</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.4008036436588692</v>
+        <v>0.4083569126728877</v>
       </c>
       <c r="T54">
-        <v>1.744265028388109</v>
+        <v>1.781377050268707</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04970662545024218</v>
+        <v>0.04876876459269045</v>
       </c>
       <c r="W54">
-        <v>0.2240791777188329</v>
+        <v>0.2243003253090436</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1420189298578348</v>
+        <v>0.139339327407687</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.3108069213700503</v>
+        <v>0.3127069213700503</v>
       </c>
       <c r="C55">
-        <v>5.570014474610034</v>
+        <v>5.072922696481939</v>
       </c>
       <c r="D55">
-        <v>20.94401447461003</v>
+        <v>20.79492269648194</v>
       </c>
       <c r="E55">
-        <v>18.444</v>
+        <v>18.792</v>
       </c>
       <c r="F55">
-        <v>18.444</v>
+        <v>18.792</v>
       </c>
       <c r="G55">
         <v>3.07</v>
@@ -5791,37 +5791,37 @@
         <v>0.606</v>
       </c>
       <c r="M55">
-        <v>4.3490952</v>
+        <v>4.4311536</v>
       </c>
       <c r="N55">
-        <v>-3.7430952</v>
+        <v>-3.8251536</v>
       </c>
       <c r="O55">
-        <v>-1.31008332</v>
+        <v>-1.33880376</v>
       </c>
       <c r="P55">
-        <v>-2.43301188</v>
+        <v>-2.48634984</v>
       </c>
       <c r="Q55">
-        <v>-2.00901188</v>
+        <v>-2.06234984</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.4083569126728877</v>
+        <v>0.4162385846875156</v>
       </c>
       <c r="T55">
-        <v>1.781377050268707</v>
+        <v>1.820102638318026</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04876876459269045</v>
+        <v>0.04786563932245544</v>
       </c>
       <c r="W55">
-        <v>0.2243003253090436</v>
+        <v>0.224513282247765</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.139339327407687</v>
+        <v>0.1367589694927298</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.3127069213700503</v>
+        <v>0.3146069213700503</v>
       </c>
       <c r="C56">
-        <v>5.072922696481939</v>
+        <v>4.577938560352028</v>
       </c>
       <c r="D56">
-        <v>20.79492269648194</v>
+        <v>20.64793856035203</v>
       </c>
       <c r="E56">
-        <v>18.792</v>
+        <v>19.14</v>
       </c>
       <c r="F56">
-        <v>18.792</v>
+        <v>19.14</v>
       </c>
       <c r="G56">
         <v>3.07</v>
@@ -5873,37 +5873,37 @@
         <v>0.606</v>
       </c>
       <c r="M56">
-        <v>4.4311536</v>
+        <v>4.513212</v>
       </c>
       <c r="N56">
-        <v>-3.8251536</v>
+        <v>-3.907212</v>
       </c>
       <c r="O56">
-        <v>-1.33880376</v>
+        <v>-1.3675242</v>
       </c>
       <c r="P56">
-        <v>-2.48634984</v>
+        <v>-2.5396878</v>
       </c>
       <c r="Q56">
-        <v>-2.06234984</v>
+        <v>-2.1156878</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.4162385846875156</v>
+        <v>0.4244705532361271</v>
       </c>
       <c r="T56">
-        <v>1.820102638318026</v>
+        <v>1.860549363613983</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04786563932245544</v>
+        <v>0.04699535497113807</v>
       </c>
       <c r="W56">
-        <v>0.224513282247765</v>
+        <v>0.2247184952978057</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1367589694927298</v>
+        <v>0.1342724427746802</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.3146069213700503</v>
+        <v>0.3165069213700503</v>
       </c>
       <c r="C57">
-        <v>4.577938560352028</v>
+        <v>4.085017687748852</v>
       </c>
       <c r="D57">
-        <v>20.64793856035203</v>
+        <v>20.50301768774885</v>
       </c>
       <c r="E57">
-        <v>19.14</v>
+        <v>19.488</v>
       </c>
       <c r="F57">
-        <v>19.14</v>
+        <v>19.488</v>
       </c>
       <c r="G57">
         <v>3.07</v>
@@ -5955,37 +5955,37 @@
         <v>0.606</v>
       </c>
       <c r="M57">
-        <v>4.513212</v>
+        <v>4.5952704</v>
       </c>
       <c r="N57">
-        <v>-3.907212</v>
+        <v>-3.989270400000001</v>
       </c>
       <c r="O57">
-        <v>-1.3675242</v>
+        <v>-1.39624464</v>
       </c>
       <c r="P57">
-        <v>-2.5396878</v>
+        <v>-2.593025760000001</v>
       </c>
       <c r="Q57">
-        <v>-2.1156878</v>
+        <v>-2.169025760000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.4244705532361271</v>
+        <v>0.4330767021733118</v>
       </c>
       <c r="T57">
-        <v>1.860549363613983</v>
+        <v>1.902834576423391</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04699535497113807</v>
+        <v>0.04615615220379631</v>
       </c>
       <c r="W57">
-        <v>0.2247184952978057</v>
+        <v>0.2249163793103448</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1342724427746802</v>
+        <v>0.1318747205822751</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.3165069213700503</v>
+        <v>0.3184069213700503</v>
       </c>
       <c r="C58">
-        <v>4.085017687748852</v>
+        <v>3.594116937426946</v>
       </c>
       <c r="D58">
-        <v>20.50301768774885</v>
+        <v>20.36011693742695</v>
       </c>
       <c r="E58">
-        <v>19.488</v>
+        <v>19.836</v>
       </c>
       <c r="F58">
-        <v>19.488</v>
+        <v>19.836</v>
       </c>
       <c r="G58">
         <v>3.07</v>
@@ -6037,37 +6037,37 @@
         <v>0.606</v>
       </c>
       <c r="M58">
-        <v>4.5952704</v>
+        <v>4.677328800000001</v>
       </c>
       <c r="N58">
-        <v>-3.989270400000001</v>
+        <v>-4.071328800000001</v>
       </c>
       <c r="O58">
-        <v>-1.39624464</v>
+        <v>-1.42496508</v>
       </c>
       <c r="P58">
-        <v>-2.593025760000001</v>
+        <v>-2.646363720000001</v>
       </c>
       <c r="Q58">
-        <v>-2.169025760000001</v>
+        <v>-2.222363720000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.4330767021733118</v>
+        <v>0.4420831371075749</v>
       </c>
       <c r="T58">
-        <v>1.902834576423391</v>
+        <v>1.947086543316959</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.04615615220379631</v>
+        <v>0.04534639514758936</v>
       </c>
       <c r="W58">
-        <v>0.2249163793103448</v>
+        <v>0.2251073200241984</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1318747205822751</v>
+        <v>0.1295611289931125</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.3184069213700503</v>
+        <v>0.3203069213700503</v>
       </c>
       <c r="C59">
-        <v>3.594116937426946</v>
+        <v>3.105194362549632</v>
       </c>
       <c r="D59">
-        <v>20.36011693742695</v>
+        <v>20.21919436254963</v>
       </c>
       <c r="E59">
-        <v>19.836</v>
+        <v>20.184</v>
       </c>
       <c r="F59">
-        <v>19.836</v>
+        <v>20.184</v>
       </c>
       <c r="G59">
         <v>3.07</v>
@@ -6119,37 +6119,37 @@
         <v>0.606</v>
       </c>
       <c r="M59">
-        <v>4.677328800000001</v>
+        <v>4.759387200000001</v>
       </c>
       <c r="N59">
-        <v>-4.071328800000001</v>
+        <v>-4.153387200000001</v>
       </c>
       <c r="O59">
-        <v>-1.42496508</v>
+        <v>-1.45368552</v>
       </c>
       <c r="P59">
-        <v>-2.646363720000001</v>
+        <v>-2.69970168</v>
       </c>
       <c r="Q59">
-        <v>-2.222363720000001</v>
+        <v>-2.275701680000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.4420831371075749</v>
+        <v>0.4515184498958505</v>
       </c>
       <c r="T59">
-        <v>1.947086543316959</v>
+        <v>1.993445746729267</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04534639514758936</v>
+        <v>0.04456456074849299</v>
       </c>
       <c r="W59">
-        <v>0.2251073200241984</v>
+        <v>0.2252916765755054</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1295611289931125</v>
+        <v>0.1273273164242656</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.3203069213700502</v>
+        <v>0.3222069213700503</v>
       </c>
       <c r="C60">
-        <v>3.105194362549646</v>
+        <v>2.618209169637584</v>
       </c>
       <c r="D60">
-        <v>20.21919436254964</v>
+        <v>20.08020916963758</v>
       </c>
       <c r="E60">
-        <v>20.184</v>
+        <v>20.532</v>
       </c>
       <c r="F60">
-        <v>20.184</v>
+        <v>20.532</v>
       </c>
       <c r="G60">
         <v>3.07</v>
@@ -6201,37 +6201,37 @@
         <v>0.606</v>
       </c>
       <c r="M60">
-        <v>4.7593872</v>
+        <v>4.841445599999999</v>
       </c>
       <c r="N60">
-        <v>-4.1533872</v>
+        <v>-4.235445599999999</v>
       </c>
       <c r="O60">
-        <v>-1.45368552</v>
+        <v>-1.48240596</v>
       </c>
       <c r="P60">
-        <v>-2.69970168</v>
+        <v>-2.75303964</v>
       </c>
       <c r="Q60">
-        <v>-2.275701680000001</v>
+        <v>-2.32903964</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.4515184498958503</v>
+        <v>0.4614140218445297</v>
       </c>
       <c r="T60">
-        <v>1.993445746729267</v>
+        <v>2.042066374698273</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04456456074849299</v>
+        <v>0.04380922921038295</v>
       </c>
       <c r="W60">
-        <v>0.2252916765755054</v>
+        <v>0.2254697837521917</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1273273164242656</v>
+        <v>0.1251692263153799</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.3222069213700503</v>
+        <v>0.3241069213700503</v>
       </c>
       <c r="C61">
-        <v>2.618209169637584</v>
+        <v>2.133121679198993</v>
       </c>
       <c r="D61">
-        <v>20.08020916963758</v>
+        <v>19.94312167919899</v>
       </c>
       <c r="E61">
-        <v>20.532</v>
+        <v>20.88</v>
       </c>
       <c r="F61">
-        <v>20.532</v>
+        <v>20.88</v>
       </c>
       <c r="G61">
         <v>3.07</v>
@@ -6283,37 +6283,37 @@
         <v>0.606</v>
       </c>
       <c r="M61">
-        <v>4.841445599999999</v>
+        <v>4.923504</v>
       </c>
       <c r="N61">
-        <v>-4.235445599999999</v>
+        <v>-4.317504</v>
       </c>
       <c r="O61">
-        <v>-1.48240596</v>
+        <v>-1.5111264</v>
       </c>
       <c r="P61">
-        <v>-2.75303964</v>
+        <v>-2.8063776</v>
       </c>
       <c r="Q61">
-        <v>-2.32903964</v>
+        <v>-2.3823776</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.4614140218445297</v>
+        <v>0.4718043723906429</v>
       </c>
       <c r="T61">
-        <v>2.042066374698273</v>
+        <v>2.09311803406573</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04380922921038295</v>
+        <v>0.04307907539020989</v>
       </c>
       <c r="W61">
-        <v>0.2254697837521917</v>
+        <v>0.2256419540229885</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1251692263153799</v>
+        <v>0.1230830725434569</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.3241069213700503</v>
+        <v>0.3260069213700503</v>
       </c>
       <c r="C62">
-        <v>2.133121679198993</v>
+        <v>1.649893287961515</v>
       </c>
       <c r="D62">
-        <v>19.94312167919899</v>
+        <v>19.80789328796151</v>
       </c>
       <c r="E62">
-        <v>20.88</v>
+        <v>21.228</v>
       </c>
       <c r="F62">
-        <v>20.88</v>
+        <v>21.228</v>
       </c>
       <c r="G62">
         <v>3.07</v>
@@ -6365,37 +6365,37 @@
         <v>0.606</v>
       </c>
       <c r="M62">
-        <v>4.923504</v>
+        <v>5.0055624</v>
       </c>
       <c r="N62">
-        <v>-4.317504</v>
+        <v>-4.3995624</v>
       </c>
       <c r="O62">
-        <v>-1.5111264</v>
+        <v>-1.53984684</v>
       </c>
       <c r="P62">
-        <v>-2.8063776</v>
+        <v>-2.85971556</v>
       </c>
       <c r="Q62">
-        <v>-2.3823776</v>
+        <v>-2.43571556</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.4718043723906429</v>
+        <v>0.4827275614263005</v>
       </c>
       <c r="T62">
-        <v>2.09311803406573</v>
+        <v>2.146787727246903</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04307907539020989</v>
+        <v>0.04237286103955071</v>
       </c>
       <c r="W62">
-        <v>0.2256419540229885</v>
+        <v>0.225808479366874</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1230830725434569</v>
+        <v>0.1210653172558592</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.3260069213700503</v>
+        <v>0.3279069213700503</v>
       </c>
       <c r="C63">
-        <v>1.649893287961515</v>
+        <v>1.168486432630377</v>
       </c>
       <c r="D63">
-        <v>19.80789328796151</v>
+        <v>19.67448643263037</v>
       </c>
       <c r="E63">
-        <v>21.228</v>
+        <v>21.576</v>
       </c>
       <c r="F63">
-        <v>21.228</v>
+        <v>21.576</v>
       </c>
       <c r="G63">
         <v>3.07</v>
@@ -6447,37 +6447,37 @@
         <v>0.606</v>
       </c>
       <c r="M63">
-        <v>5.0055624</v>
+        <v>5.0876208</v>
       </c>
       <c r="N63">
-        <v>-4.3995624</v>
+        <v>-4.4816208</v>
       </c>
       <c r="O63">
-        <v>-1.53984684</v>
+        <v>-1.56856728</v>
       </c>
       <c r="P63">
-        <v>-2.85971556</v>
+        <v>-2.91305352</v>
       </c>
       <c r="Q63">
-        <v>-2.43571556</v>
+        <v>-2.48905352</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.4827275614263005</v>
+        <v>0.4942256551480452</v>
       </c>
       <c r="T63">
-        <v>2.146787727246903</v>
+        <v>2.203282141121821</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04237286103955071</v>
+        <v>0.04168942779697732</v>
       </c>
       <c r="W63">
-        <v>0.225808479366874</v>
+        <v>0.2259696329254728</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1210653172558592</v>
+        <v>0.1191126508485066</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.3279069213700503</v>
+        <v>0.3298069213700503</v>
       </c>
       <c r="C64">
-        <v>1.168486432630377</v>
+        <v>0.6888645551012296</v>
       </c>
       <c r="D64">
-        <v>19.67448643263037</v>
+        <v>19.54286455510123</v>
       </c>
       <c r="E64">
-        <v>21.576</v>
+        <v>21.924</v>
       </c>
       <c r="F64">
-        <v>21.576</v>
+        <v>21.924</v>
       </c>
       <c r="G64">
         <v>3.07</v>
@@ -6529,37 +6529,37 @@
         <v>0.606</v>
       </c>
       <c r="M64">
-        <v>5.0876208</v>
+        <v>5.1696792</v>
       </c>
       <c r="N64">
-        <v>-4.4816208</v>
+        <v>-4.5636792</v>
       </c>
       <c r="O64">
-        <v>-1.56856728</v>
+        <v>-1.59728772</v>
       </c>
       <c r="P64">
-        <v>-2.91305352</v>
+        <v>-2.96639148</v>
       </c>
       <c r="Q64">
-        <v>-2.48905352</v>
+        <v>-2.54239148</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.4942256551480452</v>
+        <v>0.5063452674493437</v>
       </c>
       <c r="T64">
-        <v>2.203282141121821</v>
+        <v>2.262830307098087</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04168942779697732</v>
+        <v>0.04102769084781895</v>
       </c>
       <c r="W64">
-        <v>0.2259696329254728</v>
+        <v>0.2261256704980843</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1191126508485066</v>
+        <v>0.1172219738509113</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.3298069213700503</v>
+        <v>0.3317069213700502</v>
       </c>
       <c r="C65">
-        <v>0.6888645551012296</v>
+        <v>0.210992069060115</v>
       </c>
       <c r="D65">
-        <v>19.54286455510123</v>
+        <v>19.41299206906011</v>
       </c>
       <c r="E65">
-        <v>21.924</v>
+        <v>22.272</v>
       </c>
       <c r="F65">
-        <v>21.924</v>
+        <v>22.272</v>
       </c>
       <c r="G65">
         <v>3.07</v>
@@ -6611,37 +6611,37 @@
         <v>0.606</v>
       </c>
       <c r="M65">
-        <v>5.1696792</v>
+        <v>5.2517376</v>
       </c>
       <c r="N65">
-        <v>-4.5636792</v>
+        <v>-4.6457376</v>
       </c>
       <c r="O65">
-        <v>-1.59728772</v>
+        <v>-1.62600816</v>
       </c>
       <c r="P65">
-        <v>-2.96639148</v>
+        <v>-3.01972944</v>
       </c>
       <c r="Q65">
-        <v>-2.54239148</v>
+        <v>-2.59572944</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.5063452674493437</v>
+        <v>0.5191381915451587</v>
       </c>
       <c r="T65">
-        <v>2.262830307098087</v>
+        <v>2.325686704517478</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04102769084781895</v>
+        <v>0.04038663317832178</v>
       </c>
       <c r="W65">
-        <v>0.2261256704980843</v>
+        <v>0.2262768318965517</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1172219738509113</v>
+        <v>0.1153903805094908</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.3317069213700502</v>
+        <v>0.3336069213700503</v>
       </c>
       <c r="C66">
-        <v>0.210992069060115</v>
+        <v>-0.265165672093687</v>
       </c>
       <c r="D66">
-        <v>19.41299206906011</v>
+        <v>19.28483432790631</v>
       </c>
       <c r="E66">
-        <v>22.272</v>
+        <v>22.62</v>
       </c>
       <c r="F66">
-        <v>22.272</v>
+        <v>22.62</v>
       </c>
       <c r="G66">
         <v>3.07</v>
@@ -6693,37 +6693,37 @@
         <v>0.606</v>
       </c>
       <c r="M66">
-        <v>5.2517376</v>
+        <v>5.333796</v>
       </c>
       <c r="N66">
-        <v>-4.6457376</v>
+        <v>-4.727796</v>
       </c>
       <c r="O66">
-        <v>-1.62600816</v>
+        <v>-1.6547286</v>
       </c>
       <c r="P66">
-        <v>-3.01972944</v>
+        <v>-3.0730674</v>
       </c>
       <c r="Q66">
-        <v>-2.59572944</v>
+        <v>-2.6490674</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.5191381915451587</v>
+        <v>0.5326621398750205</v>
       </c>
       <c r="T66">
-        <v>2.325686704517478</v>
+        <v>2.39213489607512</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04038663317832178</v>
+        <v>0.03976530036019375</v>
       </c>
       <c r="W66">
-        <v>0.2262768318965517</v>
+        <v>0.2264233421750663</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1153903805094908</v>
+        <v>0.1136151438862678</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.3336069213700503</v>
+        <v>0.3355069213700503</v>
       </c>
       <c r="C67">
-        <v>-0.265165672093687</v>
+        <v>-0.7396424060624263</v>
       </c>
       <c r="D67">
-        <v>19.28483432790631</v>
+        <v>19.15835759393757</v>
       </c>
       <c r="E67">
-        <v>22.62</v>
+        <v>22.968</v>
       </c>
       <c r="F67">
-        <v>22.62</v>
+        <v>22.968</v>
       </c>
       <c r="G67">
         <v>3.07</v>
@@ -6775,37 +6775,37 @@
         <v>0.606</v>
       </c>
       <c r="M67">
-        <v>5.333796</v>
+        <v>5.415854400000001</v>
       </c>
       <c r="N67">
-        <v>-4.727796</v>
+        <v>-4.809854400000001</v>
       </c>
       <c r="O67">
-        <v>-1.6547286</v>
+        <v>-1.68344904</v>
       </c>
       <c r="P67">
-        <v>-3.0730674</v>
+        <v>-3.126405360000001</v>
       </c>
       <c r="Q67">
-        <v>-2.6490674</v>
+        <v>-2.702405360000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.5326621398750205</v>
+        <v>0.5469816145772269</v>
       </c>
       <c r="T67">
-        <v>2.39213489607512</v>
+        <v>2.462491804783212</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03976530036019375</v>
+        <v>0.03916279580928172</v>
       </c>
       <c r="W67">
-        <v>0.2264233421750663</v>
+        <v>0.2265654127481714</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.1136151438862678</v>
+        <v>0.1118937023122335</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.3355069213700503</v>
+        <v>0.3374069213700502</v>
       </c>
       <c r="C68">
-        <v>-0.7396424060624263</v>
+        <v>-1.212470991260126</v>
       </c>
       <c r="D68">
-        <v>19.15835759393757</v>
+        <v>19.03352900873987</v>
       </c>
       <c r="E68">
-        <v>22.968</v>
+        <v>23.316</v>
       </c>
       <c r="F68">
-        <v>22.968</v>
+        <v>23.316</v>
       </c>
       <c r="G68">
         <v>3.07</v>
@@ -6857,37 +6857,37 @@
         <v>0.606</v>
       </c>
       <c r="M68">
-        <v>5.415854400000001</v>
+        <v>5.4979128</v>
       </c>
       <c r="N68">
-        <v>-4.809854400000001</v>
+        <v>-4.8919128</v>
       </c>
       <c r="O68">
-        <v>-1.68344904</v>
+        <v>-1.71216948</v>
       </c>
       <c r="P68">
-        <v>-3.126405360000001</v>
+        <v>-3.17974332</v>
       </c>
       <c r="Q68">
-        <v>-2.702405360000001</v>
+        <v>-2.75574332</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.5469816145772269</v>
+        <v>0.5621689362310823</v>
       </c>
       <c r="T68">
-        <v>2.462491804783212</v>
+        <v>2.537112768564522</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03916279580928172</v>
+        <v>0.03857827646884468</v>
       </c>
       <c r="W68">
-        <v>0.2265654127481714</v>
+        <v>0.2267032424086464</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1118937023122335</v>
+        <v>0.1102236470538419</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.3374069213700502</v>
+        <v>0.3393069213700503</v>
       </c>
       <c r="C69">
-        <v>-1.212470991260126</v>
+        <v>-1.683683435272695</v>
       </c>
       <c r="D69">
-        <v>19.03352900873987</v>
+        <v>18.91031656472731</v>
       </c>
       <c r="E69">
-        <v>23.316</v>
+        <v>23.664</v>
       </c>
       <c r="F69">
-        <v>23.316</v>
+        <v>23.664</v>
       </c>
       <c r="G69">
         <v>3.07</v>
@@ -6939,37 +6939,37 @@
         <v>0.606</v>
       </c>
       <c r="M69">
-        <v>5.4979128</v>
+        <v>5.579971200000001</v>
       </c>
       <c r="N69">
-        <v>-4.8919128</v>
+        <v>-4.973971200000001</v>
       </c>
       <c r="O69">
-        <v>-1.71216948</v>
+        <v>-1.74088992</v>
       </c>
       <c r="P69">
-        <v>-3.17974332</v>
+        <v>-3.233081280000001</v>
       </c>
       <c r="Q69">
-        <v>-2.75574332</v>
+        <v>-2.809081280000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.5621689362310823</v>
+        <v>0.5783054654883037</v>
       </c>
       <c r="T69">
-        <v>2.537112768564522</v>
+        <v>2.616397542582163</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03857827646884468</v>
+        <v>0.03801094887371461</v>
       </c>
       <c r="W69">
-        <v>0.2267032424086464</v>
+        <v>0.2268370182555781</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1102236470538419</v>
+        <v>0.108602711067756</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.3393069213700503</v>
+        <v>0.3412069213700503</v>
       </c>
       <c r="C70">
-        <v>-1.683683435272695</v>
+        <v>-2.15331092221966</v>
       </c>
       <c r="D70">
-        <v>18.91031656472731</v>
+        <v>18.78868907778034</v>
       </c>
       <c r="E70">
-        <v>23.664</v>
+        <v>24.012</v>
       </c>
       <c r="F70">
-        <v>23.664</v>
+        <v>24.012</v>
       </c>
       <c r="G70">
         <v>3.07</v>
@@ -7021,37 +7021,37 @@
         <v>0.606</v>
       </c>
       <c r="M70">
-        <v>5.579971200000001</v>
+        <v>5.6620296</v>
       </c>
       <c r="N70">
-        <v>-4.973971200000001</v>
+        <v>-5.0560296</v>
       </c>
       <c r="O70">
-        <v>-1.74088992</v>
+        <v>-1.76961036</v>
       </c>
       <c r="P70">
-        <v>-3.233081280000001</v>
+        <v>-3.286419240000001</v>
       </c>
       <c r="Q70">
-        <v>-2.809081280000001</v>
+        <v>-2.862419240000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.5783054654883037</v>
+        <v>0.5954830611492168</v>
       </c>
       <c r="T70">
-        <v>2.616397542582163</v>
+        <v>2.70079746331062</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03801094887371461</v>
+        <v>0.03746006555670426</v>
       </c>
       <c r="W70">
-        <v>0.2268370182555781</v>
+        <v>0.2269669165417292</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.108602711067756</v>
+        <v>0.1070287587334408</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.3412069213700503</v>
+        <v>0.3431069213700503</v>
       </c>
       <c r="C71">
-        <v>-2.15331092221966</v>
+        <v>-2.62138383906693</v>
       </c>
       <c r="D71">
-        <v>18.78868907778034</v>
+        <v>18.66861616093307</v>
       </c>
       <c r="E71">
-        <v>24.012</v>
+        <v>24.36</v>
       </c>
       <c r="F71">
-        <v>24.012</v>
+        <v>24.36</v>
       </c>
       <c r="G71">
         <v>3.07</v>
@@ -7103,37 +7103,37 @@
         <v>0.606</v>
       </c>
       <c r="M71">
-        <v>5.6620296</v>
+        <v>5.744088000000001</v>
       </c>
       <c r="N71">
-        <v>-5.0560296</v>
+        <v>-5.138088000000001</v>
       </c>
       <c r="O71">
-        <v>-1.76961036</v>
+        <v>-1.7983308</v>
       </c>
       <c r="P71">
-        <v>-3.286419240000001</v>
+        <v>-3.339757200000001</v>
       </c>
       <c r="Q71">
-        <v>-2.862419240000001</v>
+        <v>-2.915757200000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.5954830611492168</v>
+        <v>0.6138058298541905</v>
       </c>
       <c r="T71">
-        <v>2.70079746331062</v>
+        <v>2.790824045420974</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03746006555670426</v>
+        <v>0.03692492176303705</v>
       </c>
       <c r="W71">
-        <v>0.2269669165417292</v>
+        <v>0.2270931034482759</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1070287587334408</v>
+        <v>0.1054997764658201</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.3431069213700503</v>
+        <v>0.3450069213700503</v>
       </c>
       <c r="C72">
-        <v>-2.62138383906693</v>
+        <v>-3.087931800936783</v>
       </c>
       <c r="D72">
-        <v>18.66861616093307</v>
+        <v>18.55006819906322</v>
       </c>
       <c r="E72">
-        <v>24.36</v>
+        <v>24.708</v>
       </c>
       <c r="F72">
-        <v>24.36</v>
+        <v>24.708</v>
       </c>
       <c r="G72">
         <v>3.07</v>
@@ -7185,37 +7185,37 @@
         <v>0.606</v>
       </c>
       <c r="M72">
-        <v>5.744088000000001</v>
+        <v>5.826146400000001</v>
       </c>
       <c r="N72">
-        <v>-5.138088000000001</v>
+        <v>-5.220146400000001</v>
       </c>
       <c r="O72">
-        <v>-1.7983308</v>
+        <v>-1.82705124</v>
       </c>
       <c r="P72">
-        <v>-3.339757200000001</v>
+        <v>-3.393095160000001</v>
       </c>
       <c r="Q72">
-        <v>-2.915757200000001</v>
+        <v>-2.969095160000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.6138058298541905</v>
+        <v>0.6333922377801973</v>
       </c>
       <c r="T72">
-        <v>2.790824045420974</v>
+        <v>2.887059357332042</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.03692492176303705</v>
+        <v>0.03640485244243089</v>
       </c>
       <c r="W72">
-        <v>0.2270931034482759</v>
+        <v>0.2272157357940748</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1054997764658201</v>
+        <v>0.1040138641212311</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.3450069213700503</v>
+        <v>0.3469069213700502</v>
       </c>
       <c r="C73">
-        <v>-3.087931800936779</v>
+        <v>-3.552983675459799</v>
       </c>
       <c r="D73">
-        <v>18.55006819906322</v>
+        <v>18.4330163245402</v>
       </c>
       <c r="E73">
-        <v>24.708</v>
+        <v>25.056</v>
       </c>
       <c r="F73">
-        <v>24.708</v>
+        <v>25.056</v>
       </c>
       <c r="G73">
         <v>3.07</v>
@@ -7267,37 +7267,37 @@
         <v>0.606</v>
       </c>
       <c r="M73">
-        <v>5.8261464</v>
+        <v>5.9082048</v>
       </c>
       <c r="N73">
-        <v>-5.2201464</v>
+        <v>-5.3022048</v>
       </c>
       <c r="O73">
-        <v>-1.82705124</v>
+        <v>-1.85577168</v>
       </c>
       <c r="P73">
-        <v>-3.39309516</v>
+        <v>-3.44643312</v>
       </c>
       <c r="Q73">
-        <v>-2.96909516</v>
+        <v>-3.02243312</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.633392237780197</v>
+        <v>0.6543776748437755</v>
       </c>
       <c r="T73">
-        <v>2.887059357332042</v>
+        <v>2.9901686200939</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.0364048524424309</v>
+        <v>0.03589922949184158</v>
       </c>
       <c r="W73">
-        <v>0.2272157357940748</v>
+        <v>0.2273349616858238</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1040138641212311</v>
+        <v>0.1025692271195473</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.3469069213700502</v>
+        <v>0.3488069213700503</v>
       </c>
       <c r="C74">
-        <v>-3.552983675459799</v>
+        <v>-4.016567606210522</v>
       </c>
       <c r="D74">
-        <v>18.4330163245402</v>
+        <v>18.31743239378947</v>
       </c>
       <c r="E74">
-        <v>25.056</v>
+        <v>25.404</v>
       </c>
       <c r="F74">
-        <v>25.056</v>
+        <v>25.404</v>
       </c>
       <c r="G74">
         <v>3.07</v>
@@ -7349,37 +7349,37 @@
         <v>0.606</v>
       </c>
       <c r="M74">
-        <v>5.9082048</v>
+        <v>5.990263199999999</v>
       </c>
       <c r="N74">
-        <v>-5.3022048</v>
+        <v>-5.384263199999999</v>
       </c>
       <c r="O74">
-        <v>-1.85577168</v>
+        <v>-1.88449212</v>
       </c>
       <c r="P74">
-        <v>-3.44643312</v>
+        <v>-3.499771079999999</v>
       </c>
       <c r="Q74">
-        <v>-3.02243312</v>
+        <v>-3.07577108</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.6543776748437755</v>
+        <v>0.6769175887268782</v>
       </c>
       <c r="T74">
-        <v>2.9901686200939</v>
+        <v>3.100915606023304</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03589922949184158</v>
+        <v>0.03540745922483005</v>
       </c>
       <c r="W74">
-        <v>0.2273349616858238</v>
+        <v>0.2274509211147851</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1025692271195473</v>
+        <v>0.1011641692138001</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.3488069213700503</v>
+        <v>0.3507069213700503</v>
       </c>
       <c r="C75">
-        <v>-4.016567606210522</v>
+        <v>-4.478711035266901</v>
       </c>
       <c r="D75">
-        <v>18.31743239378947</v>
+        <v>18.2032889647331</v>
       </c>
       <c r="E75">
-        <v>25.404</v>
+        <v>25.752</v>
       </c>
       <c r="F75">
-        <v>25.404</v>
+        <v>25.752</v>
       </c>
       <c r="G75">
         <v>3.07</v>
@@ -7431,37 +7431,37 @@
         <v>0.606</v>
       </c>
       <c r="M75">
-        <v>5.990263199999999</v>
+        <v>6.0723216</v>
       </c>
       <c r="N75">
-        <v>-5.384263199999999</v>
+        <v>-5.4663216</v>
       </c>
       <c r="O75">
-        <v>-1.88449212</v>
+        <v>-1.91321256</v>
       </c>
       <c r="P75">
-        <v>-3.499771079999999</v>
+        <v>-3.55310904</v>
       </c>
       <c r="Q75">
-        <v>-3.07577108</v>
+        <v>-3.12910904</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.6769175887268782</v>
+        <v>0.7011913421394506</v>
       </c>
       <c r="T75">
-        <v>3.100915606023304</v>
+        <v>3.220181590870354</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03540745922483005</v>
+        <v>0.03492898004611613</v>
       </c>
       <c r="W75">
-        <v>0.2274509211147851</v>
+        <v>0.2275637465051258</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1011641692138001</v>
+        <v>0.09979708584604607</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.3507069213700503</v>
+        <v>0.3526069213700502</v>
       </c>
       <c r="C76">
-        <v>-4.478711035266901</v>
+        <v>-4.939440724931487</v>
       </c>
       <c r="D76">
-        <v>18.2032889647331</v>
+        <v>18.09055927506851</v>
       </c>
       <c r="E76">
-        <v>25.752</v>
+        <v>26.1</v>
       </c>
       <c r="F76">
-        <v>25.752</v>
+        <v>26.1</v>
       </c>
       <c r="G76">
         <v>3.07</v>
@@ -7513,37 +7513,37 @@
         <v>0.606</v>
       </c>
       <c r="M76">
-        <v>6.0723216</v>
+        <v>6.15438</v>
       </c>
       <c r="N76">
-        <v>-5.4663216</v>
+        <v>-5.54838</v>
       </c>
       <c r="O76">
-        <v>-1.91321256</v>
+        <v>-1.941933</v>
       </c>
       <c r="P76">
-        <v>-3.55310904</v>
+        <v>-3.606447</v>
       </c>
       <c r="Q76">
-        <v>-3.12910904</v>
+        <v>-3.182447</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.7011913421394506</v>
+        <v>0.7274069958250287</v>
       </c>
       <c r="T76">
-        <v>3.220181590870354</v>
+        <v>3.348988854505168</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03492898004611613</v>
+        <v>0.03446326031216792</v>
       </c>
       <c r="W76">
-        <v>0.2275637465051258</v>
+        <v>0.2276735632183908</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.09979708584604607</v>
+        <v>0.0984664580347655</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.3526069213700502</v>
+        <v>0.3545069213700503</v>
       </c>
       <c r="C77">
-        <v>-4.939440724931487</v>
+        <v>-5.398782778650553</v>
       </c>
       <c r="D77">
-        <v>18.09055927506851</v>
+        <v>17.97921722134944</v>
       </c>
       <c r="E77">
-        <v>26.1</v>
+        <v>26.448</v>
       </c>
       <c r="F77">
-        <v>26.1</v>
+        <v>26.448</v>
       </c>
       <c r="G77">
         <v>3.07</v>
@@ -7595,37 +7595,37 @@
         <v>0.606</v>
       </c>
       <c r="M77">
-        <v>6.15438</v>
+        <v>6.2364384</v>
       </c>
       <c r="N77">
-        <v>-5.54838</v>
+        <v>-5.6304384</v>
       </c>
       <c r="O77">
-        <v>-1.941933</v>
+        <v>-1.97065344</v>
       </c>
       <c r="P77">
-        <v>-3.606447</v>
+        <v>-3.65978496</v>
       </c>
       <c r="Q77">
-        <v>-3.182447</v>
+        <v>-3.23578496</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.7274069958250287</v>
+        <v>0.7558072873177383</v>
       </c>
       <c r="T77">
-        <v>3.348988854505168</v>
+        <v>3.488530056776217</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03446326031216792</v>
+        <v>0.03400979636069202</v>
       </c>
       <c r="W77">
-        <v>0.2276735632183908</v>
+        <v>0.2277804900181488</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.0984664580347655</v>
+        <v>0.09717084674483434</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.3545069213700503</v>
+        <v>0.3564069213700503</v>
       </c>
       <c r="C78">
-        <v>-5.398782778650553</v>
+        <v>-5.856762661165359</v>
       </c>
       <c r="D78">
-        <v>17.97921722134944</v>
+        <v>17.86923733883464</v>
       </c>
       <c r="E78">
-        <v>26.448</v>
+        <v>26.796</v>
       </c>
       <c r="F78">
-        <v>26.448</v>
+        <v>26.796</v>
       </c>
       <c r="G78">
         <v>3.07</v>
@@ -7677,37 +7677,37 @@
         <v>0.606</v>
       </c>
       <c r="M78">
-        <v>6.2364384</v>
+        <v>6.3184968</v>
       </c>
       <c r="N78">
-        <v>-5.6304384</v>
+        <v>-5.7124968</v>
       </c>
       <c r="O78">
-        <v>-1.97065344</v>
+        <v>-1.99937388</v>
       </c>
       <c r="P78">
-        <v>-3.65978496</v>
+        <v>-3.71312292</v>
       </c>
       <c r="Q78">
-        <v>-3.23578496</v>
+        <v>-3.28912292</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.7558072873177383</v>
+        <v>0.7866771693750313</v>
       </c>
       <c r="T78">
-        <v>3.488530056776217</v>
+        <v>3.640205276636053</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.03400979636069202</v>
+        <v>0.03356811069367004</v>
       </c>
       <c r="W78">
-        <v>0.2277804900181488</v>
+        <v>0.2278846394984326</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.09717084674483434</v>
+        <v>0.0959088876962001</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.3564069213700503</v>
+        <v>0.3583069213700503</v>
       </c>
       <c r="C79">
-        <v>-5.856762661165359</v>
+        <v>-6.313405217928388</v>
       </c>
       <c r="D79">
-        <v>17.86923733883464</v>
+        <v>17.76059478207161</v>
       </c>
       <c r="E79">
-        <v>26.796</v>
+        <v>27.144</v>
       </c>
       <c r="F79">
-        <v>26.796</v>
+        <v>27.144</v>
       </c>
       <c r="G79">
         <v>3.07</v>
@@ -7759,37 +7759,37 @@
         <v>0.606</v>
       </c>
       <c r="M79">
-        <v>6.3184968</v>
+        <v>6.400555199999999</v>
       </c>
       <c r="N79">
-        <v>-5.7124968</v>
+        <v>-5.7945552</v>
       </c>
       <c r="O79">
-        <v>-1.99937388</v>
+        <v>-2.02809432</v>
       </c>
       <c r="P79">
-        <v>-3.71312292</v>
+        <v>-3.76646088</v>
       </c>
       <c r="Q79">
-        <v>-3.28912292</v>
+        <v>-3.34246088</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.7866771693750313</v>
+        <v>0.8203534043466235</v>
       </c>
       <c r="T79">
-        <v>3.640205276636053</v>
+        <v>3.805669152846782</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03356811069367004</v>
+        <v>0.03313775030016146</v>
       </c>
       <c r="W79">
-        <v>0.2278846394984326</v>
+        <v>0.227986118479222</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.0959088876962001</v>
+        <v>0.09467928657188984</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.3583069213700503</v>
+        <v>0.3602069213700503</v>
       </c>
       <c r="C80">
-        <v>-6.313405217928388</v>
+        <v>-6.768734693815524</v>
       </c>
       <c r="D80">
-        <v>17.76059478207161</v>
+        <v>17.65326530618447</v>
       </c>
       <c r="E80">
-        <v>27.144</v>
+        <v>27.492</v>
       </c>
       <c r="F80">
-        <v>27.144</v>
+        <v>27.492</v>
       </c>
       <c r="G80">
         <v>3.07</v>
@@ -7841,37 +7841,37 @@
         <v>0.606</v>
       </c>
       <c r="M80">
-        <v>6.400555199999999</v>
+        <v>6.4826136</v>
       </c>
       <c r="N80">
-        <v>-5.7945552</v>
+        <v>-5.8766136</v>
       </c>
       <c r="O80">
-        <v>-2.02809432</v>
+        <v>-2.05681476</v>
       </c>
       <c r="P80">
-        <v>-3.76646088</v>
+        <v>-3.81979884</v>
       </c>
       <c r="Q80">
-        <v>-3.34246088</v>
+        <v>-3.39579884</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.8203534043466235</v>
+        <v>0.8572368997917009</v>
       </c>
       <c r="T80">
-        <v>3.805669152846782</v>
+        <v>3.986891493458534</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03313775030016146</v>
+        <v>0.03271828510648853</v>
       </c>
       <c r="W80">
-        <v>0.227986118479222</v>
+        <v>0.22808502837189</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.09467928657188984</v>
+        <v>0.09348081458996726</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.3602069213700503</v>
+        <v>0.3621069213700503</v>
       </c>
       <c r="C81">
-        <v>-6.768734693815524</v>
+        <v>-7.222774751163843</v>
       </c>
       <c r="D81">
-        <v>17.65326530618447</v>
+        <v>17.54722524883616</v>
       </c>
       <c r="E81">
-        <v>27.492</v>
+        <v>27.84</v>
       </c>
       <c r="F81">
-        <v>27.492</v>
+        <v>27.84</v>
       </c>
       <c r="G81">
         <v>3.07</v>
@@ -7923,37 +7923,37 @@
         <v>0.606</v>
       </c>
       <c r="M81">
-        <v>6.4826136</v>
+        <v>6.564672</v>
       </c>
       <c r="N81">
-        <v>-5.8766136</v>
+        <v>-5.958672</v>
       </c>
       <c r="O81">
-        <v>-2.05681476</v>
+        <v>-2.0855352</v>
       </c>
       <c r="P81">
-        <v>-3.81979884</v>
+        <v>-3.8731368</v>
       </c>
       <c r="Q81">
-        <v>-3.39579884</v>
+        <v>-3.4491368</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.8572368997917009</v>
+        <v>0.897808744781286</v>
       </c>
       <c r="T81">
-        <v>3.986891493458534</v>
+        <v>4.186236068131461</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.03271828510648853</v>
+        <v>0.03230930654265742</v>
       </c>
       <c r="W81">
-        <v>0.22808502837189</v>
+        <v>0.2281814655172414</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.09348081458996726</v>
+        <v>0.09231230440759264</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.3621069213700503</v>
+        <v>0.3640069213700503</v>
       </c>
       <c r="C82">
-        <v>-7.222774751163843</v>
+        <v>-7.675548487163191</v>
       </c>
       <c r="D82">
-        <v>17.54722524883616</v>
+        <v>17.44245151283681</v>
       </c>
       <c r="E82">
-        <v>27.84</v>
+        <v>28.188</v>
       </c>
       <c r="F82">
-        <v>27.84</v>
+        <v>28.188</v>
       </c>
       <c r="G82">
         <v>3.07</v>
@@ -8005,37 +8005,37 @@
         <v>0.606</v>
       </c>
       <c r="M82">
-        <v>6.564672</v>
+        <v>6.6467304</v>
       </c>
       <c r="N82">
-        <v>-5.958672</v>
+        <v>-6.0407304</v>
       </c>
       <c r="O82">
-        <v>-2.0855352</v>
+        <v>-2.11425564</v>
       </c>
       <c r="P82">
-        <v>-3.8731368</v>
+        <v>-3.92647476</v>
       </c>
       <c r="Q82">
-        <v>-3.4491368</v>
+        <v>-3.50247476</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.897808744781286</v>
+        <v>0.9426513102960906</v>
       </c>
       <c r="T82">
-        <v>4.186236068131461</v>
+        <v>4.406564282243644</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03230930654265742</v>
+        <v>0.03191042621497029</v>
       </c>
       <c r="W82">
-        <v>0.2281814655172414</v>
+        <v>0.22827552149851</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.09231230440759264</v>
+        <v>0.09117264632848654</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.3640069213700503</v>
+        <v>0.3659069213700503</v>
       </c>
       <c r="C83">
-        <v>-7.675548487163191</v>
+        <v>-8.12707845062836</v>
       </c>
       <c r="D83">
-        <v>17.44245151283681</v>
+        <v>17.33892154937164</v>
       </c>
       <c r="E83">
-        <v>28.188</v>
+        <v>28.536</v>
       </c>
       <c r="F83">
-        <v>28.188</v>
+        <v>28.536</v>
       </c>
       <c r="G83">
         <v>3.07</v>
@@ -8087,37 +8087,37 @@
         <v>0.606</v>
       </c>
       <c r="M83">
-        <v>6.6467304</v>
+        <v>6.7287888</v>
       </c>
       <c r="N83">
-        <v>-6.0407304</v>
+        <v>-6.1227888</v>
       </c>
       <c r="O83">
-        <v>-2.11425564</v>
+        <v>-2.14297608</v>
       </c>
       <c r="P83">
-        <v>-3.92647476</v>
+        <v>-3.97981272</v>
       </c>
       <c r="Q83">
-        <v>-3.50247476</v>
+        <v>-3.55581272</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.9426513102960906</v>
+        <v>0.9924763830903178</v>
       </c>
       <c r="T83">
-        <v>4.406564282243644</v>
+        <v>4.651373409034957</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03191042621497029</v>
+        <v>0.03152127467576334</v>
       </c>
       <c r="W83">
-        <v>0.22827552149851</v>
+        <v>0.228367283431455</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.09117264632848654</v>
+        <v>0.09006078478789525</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.3659069213700503</v>
+        <v>0.3678069213700503</v>
       </c>
       <c r="C84">
-        <v>-8.12707845062836</v>
+        <v>-8.577386658177563</v>
       </c>
       <c r="D84">
-        <v>17.33892154937164</v>
+        <v>17.23661334182244</v>
       </c>
       <c r="E84">
-        <v>28.536</v>
+        <v>28.884</v>
       </c>
       <c r="F84">
-        <v>28.536</v>
+        <v>28.884</v>
       </c>
       <c r="G84">
         <v>3.07</v>
@@ -8169,37 +8169,37 @@
         <v>0.606</v>
       </c>
       <c r="M84">
-        <v>6.7287888</v>
+        <v>6.8108472</v>
       </c>
       <c r="N84">
-        <v>-6.1227888</v>
+        <v>-6.204847200000001</v>
       </c>
       <c r="O84">
-        <v>-2.14297608</v>
+        <v>-2.17169652</v>
       </c>
       <c r="P84">
-        <v>-3.97981272</v>
+        <v>-4.03315068</v>
       </c>
       <c r="Q84">
-        <v>-3.55581272</v>
+        <v>-3.60915068</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.9924763830903178</v>
+        <v>1.048163229154454</v>
       </c>
       <c r="T84">
-        <v>4.651373409034957</v>
+        <v>4.924983609566426</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03152127467576334</v>
+        <v>0.03114150028207944</v>
       </c>
       <c r="W84">
-        <v>0.228367283431455</v>
+        <v>0.2284568342334857</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.09006078478789525</v>
+        <v>0.08897571509165558</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.3678069213700503</v>
+        <v>0.3697069213700503</v>
       </c>
       <c r="C85">
-        <v>-8.577386658177563</v>
+        <v>-9.026494609841393</v>
       </c>
       <c r="D85">
-        <v>17.23661334182244</v>
+        <v>17.13550539015861</v>
       </c>
       <c r="E85">
-        <v>28.884</v>
+        <v>29.232</v>
       </c>
       <c r="F85">
-        <v>28.884</v>
+        <v>29.232</v>
       </c>
       <c r="G85">
         <v>3.07</v>
@@ -8251,37 +8251,37 @@
         <v>0.606</v>
       </c>
       <c r="M85">
-        <v>6.8108472</v>
+        <v>6.8929056</v>
       </c>
       <c r="N85">
-        <v>-6.204847200000001</v>
+        <v>-6.2869056</v>
       </c>
       <c r="O85">
-        <v>-2.17169652</v>
+        <v>-2.20041696</v>
       </c>
       <c r="P85">
-        <v>-4.03315068</v>
+        <v>-4.086488640000001</v>
       </c>
       <c r="Q85">
-        <v>-3.60915068</v>
+        <v>-3.662488640000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>1.048163229154454</v>
+        <v>1.110810930976608</v>
       </c>
       <c r="T85">
-        <v>4.924983609566426</v>
+        <v>5.232795085164328</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.03114150028207944</v>
+        <v>0.03077076813586421</v>
       </c>
       <c r="W85">
-        <v>0.2284568342334857</v>
+        <v>0.2285442528735632</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.08897571509165558</v>
+        <v>0.08791648038818345</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.3697069213700503</v>
+        <v>0.3716069213700504</v>
       </c>
       <c r="C86">
-        <v>-9.026494609841382</v>
+        <v>-9.474423304125708</v>
       </c>
       <c r="D86">
-        <v>17.13550539015861</v>
+        <v>17.03557669587429</v>
       </c>
       <c r="E86">
-        <v>29.232</v>
+        <v>29.58</v>
       </c>
       <c r="F86">
-        <v>29.232</v>
+        <v>29.58</v>
       </c>
       <c r="G86">
         <v>3.07</v>
@@ -8333,37 +8333,37 @@
         <v>0.606</v>
       </c>
       <c r="M86">
-        <v>6.892905599999999</v>
+        <v>6.974964</v>
       </c>
       <c r="N86">
-        <v>-6.286905599999999</v>
+        <v>-6.368964</v>
       </c>
       <c r="O86">
-        <v>-2.20041696</v>
+        <v>-2.2291374</v>
       </c>
       <c r="P86">
-        <v>-4.086488639999999</v>
+        <v>-4.1398266</v>
       </c>
       <c r="Q86">
-        <v>-3.662488639999999</v>
+        <v>-3.7158266</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>1.110810930976607</v>
+        <v>1.181811659708381</v>
       </c>
       <c r="T86">
-        <v>5.232795085164325</v>
+        <v>5.581648090841947</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.03077076813586422</v>
+        <v>0.03040875909897169</v>
       </c>
       <c r="W86">
-        <v>0.2285442528735632</v>
+        <v>0.2286296146044625</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.08791648038818345</v>
+        <v>0.08688216885420486</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.3716069213700504</v>
+        <v>0.3735069213700503</v>
       </c>
       <c r="C87">
-        <v>-9.474423304125708</v>
+        <v>-9.921193252550474</v>
       </c>
       <c r="D87">
-        <v>17.03557669587429</v>
+        <v>16.93680674744952</v>
       </c>
       <c r="E87">
-        <v>29.58</v>
+        <v>29.928</v>
       </c>
       <c r="F87">
-        <v>29.58</v>
+        <v>29.928</v>
       </c>
       <c r="G87">
         <v>3.07</v>
@@ -8415,37 +8415,37 @@
         <v>0.606</v>
       </c>
       <c r="M87">
-        <v>6.974964</v>
+        <v>7.057022399999999</v>
       </c>
       <c r="N87">
-        <v>-6.368964</v>
+        <v>-6.451022399999999</v>
       </c>
       <c r="O87">
-        <v>-2.2291374</v>
+        <v>-2.25785784</v>
       </c>
       <c r="P87">
-        <v>-4.1398266</v>
+        <v>-4.19316456</v>
       </c>
       <c r="Q87">
-        <v>-3.7158266</v>
+        <v>-3.76916456</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>1.181811659708381</v>
+        <v>1.262955349687551</v>
       </c>
       <c r="T87">
-        <v>5.581648090841947</v>
+        <v>5.9803372401878</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03040875909897169</v>
+        <v>0.03005516887689063</v>
       </c>
       <c r="W87">
-        <v>0.2286296146044625</v>
+        <v>0.2287129911788292</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.08688216885420486</v>
+        <v>0.08587191107683034</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.3735069213700503</v>
+        <v>0.3754069213700503</v>
       </c>
       <c r="C88">
-        <v>-9.921193252550474</v>
+        <v>-10.36682449368581</v>
       </c>
       <c r="D88">
-        <v>16.93680674744952</v>
+        <v>16.83917550631419</v>
       </c>
       <c r="E88">
-        <v>29.928</v>
+        <v>30.276</v>
       </c>
       <c r="F88">
-        <v>29.928</v>
+        <v>30.276</v>
       </c>
       <c r="G88">
         <v>3.07</v>
@@ -8497,37 +8497,37 @@
         <v>0.606</v>
       </c>
       <c r="M88">
-        <v>7.057022399999999</v>
+        <v>7.139080799999999</v>
       </c>
       <c r="N88">
-        <v>-6.451022399999999</v>
+        <v>-6.5330808</v>
       </c>
       <c r="O88">
-        <v>-2.25785784</v>
+        <v>-2.28657828</v>
       </c>
       <c r="P88">
-        <v>-4.19316456</v>
+        <v>-4.24650252</v>
       </c>
       <c r="Q88">
-        <v>-3.76916456</v>
+        <v>-3.82250252</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>1.262955349687551</v>
+        <v>1.356582684278901</v>
       </c>
       <c r="T88">
-        <v>5.9803372401878</v>
+        <v>6.440363181740707</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03005516887689063</v>
+        <v>0.029709707165662</v>
       </c>
       <c r="W88">
-        <v>0.2287129911788292</v>
+        <v>0.2287944510503369</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.08587191107683034</v>
+        <v>0.08488487761617713</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.3754069213700503</v>
+        <v>0.3773069213700503</v>
       </c>
       <c r="C89">
-        <v>-10.36682449368581</v>
+        <v>-10.81133660670526</v>
       </c>
       <c r="D89">
-        <v>16.83917550631419</v>
+        <v>16.74266339329474</v>
       </c>
       <c r="E89">
-        <v>30.276</v>
+        <v>30.624</v>
       </c>
       <c r="F89">
-        <v>30.276</v>
+        <v>30.624</v>
       </c>
       <c r="G89">
         <v>3.07</v>
@@ -8579,37 +8579,37 @@
         <v>0.606</v>
       </c>
       <c r="M89">
-        <v>7.139080799999999</v>
+        <v>7.2211392</v>
       </c>
       <c r="N89">
-        <v>-6.5330808</v>
+        <v>-6.6151392</v>
       </c>
       <c r="O89">
-        <v>-2.28657828</v>
+        <v>-2.31529872</v>
       </c>
       <c r="P89">
-        <v>-4.24650252</v>
+        <v>-4.29984048</v>
       </c>
       <c r="Q89">
-        <v>-3.82250252</v>
+        <v>-3.87584048</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>1.356582684278901</v>
+        <v>1.465814574635477</v>
       </c>
       <c r="T89">
-        <v>6.440363181740707</v>
+        <v>6.977060113552435</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.029709707165662</v>
+        <v>0.02937209685696129</v>
       </c>
       <c r="W89">
-        <v>0.2287944510503369</v>
+        <v>0.2288740595611285</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.08488487761617713</v>
+        <v>0.08392027673417513</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.3773069213700503</v>
+        <v>0.3792069213700503</v>
       </c>
       <c r="C90">
-        <v>-10.81133660670526</v>
+        <v>-11.25474872447576</v>
       </c>
       <c r="D90">
-        <v>16.74266339329474</v>
+        <v>16.64725127552424</v>
       </c>
       <c r="E90">
-        <v>30.624</v>
+        <v>30.972</v>
       </c>
       <c r="F90">
-        <v>30.624</v>
+        <v>30.972</v>
       </c>
       <c r="G90">
         <v>3.07</v>
@@ -8661,37 +8661,37 @@
         <v>0.606</v>
       </c>
       <c r="M90">
-        <v>7.2211392</v>
+        <v>7.3031976</v>
       </c>
       <c r="N90">
-        <v>-6.6151392</v>
+        <v>-6.6971976</v>
       </c>
       <c r="O90">
-        <v>-2.31529872</v>
+        <v>-2.34401916</v>
       </c>
       <c r="P90">
-        <v>-4.29984048</v>
+        <v>-4.353178440000001</v>
       </c>
       <c r="Q90">
-        <v>-3.87584048</v>
+        <v>-3.929178440000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>1.465814574635477</v>
+        <v>1.594906808693247</v>
       </c>
       <c r="T90">
-        <v>6.977060113552435</v>
+        <v>7.611338305693565</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02937209685696129</v>
+        <v>0.02904207329677072</v>
       </c>
       <c r="W90">
-        <v>0.2288740595611285</v>
+        <v>0.2289518791166215</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.08392027673417513</v>
+        <v>0.08297735227648773</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.3792069213700503</v>
+        <v>0.3811069213700503</v>
       </c>
       <c r="C91">
-        <v>-11.25474872447576</v>
+        <v>-11.69707954620249</v>
       </c>
       <c r="D91">
-        <v>16.64725127552424</v>
+        <v>16.55292045379751</v>
       </c>
       <c r="E91">
-        <v>30.972</v>
+        <v>31.32</v>
       </c>
       <c r="F91">
-        <v>30.972</v>
+        <v>31.32</v>
       </c>
       <c r="G91">
         <v>3.07</v>
@@ -8743,37 +8743,37 @@
         <v>0.606</v>
       </c>
       <c r="M91">
-        <v>7.3031976</v>
+        <v>7.385255999999999</v>
       </c>
       <c r="N91">
-        <v>-6.6971976</v>
+        <v>-6.779255999999999</v>
       </c>
       <c r="O91">
-        <v>-2.34401916</v>
+        <v>-2.3727396</v>
       </c>
       <c r="P91">
-        <v>-4.353178440000001</v>
+        <v>-4.406516399999999</v>
       </c>
       <c r="Q91">
-        <v>-3.929178440000001</v>
+        <v>-3.982516399999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.594906808693247</v>
+        <v>1.749817489562572</v>
       </c>
       <c r="T91">
-        <v>7.611338305693565</v>
+        <v>8.372472136262923</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02904207329677072</v>
+        <v>0.02871938359347326</v>
       </c>
       <c r="W91">
-        <v>0.2289518791166215</v>
+        <v>0.229027969348659</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.08297735227648773</v>
+        <v>0.08205538169563786</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.3811069213700503</v>
+        <v>0.3830069213700503</v>
       </c>
       <c r="C92">
-        <v>-11.69707954620249</v>
+        <v>-12.13834734964625</v>
       </c>
       <c r="D92">
-        <v>16.55292045379751</v>
+        <v>16.45965265035375</v>
       </c>
       <c r="E92">
-        <v>31.32</v>
+        <v>31.668</v>
       </c>
       <c r="F92">
-        <v>31.32</v>
+        <v>31.668</v>
       </c>
       <c r="G92">
         <v>3.07</v>
@@ -8825,37 +8825,37 @@
         <v>0.606</v>
       </c>
       <c r="M92">
-        <v>7.385255999999999</v>
+        <v>7.4673144</v>
       </c>
       <c r="N92">
-        <v>-6.779255999999999</v>
+        <v>-6.8613144</v>
       </c>
       <c r="O92">
-        <v>-2.3727396</v>
+        <v>-2.40146004</v>
       </c>
       <c r="P92">
-        <v>-4.406516399999999</v>
+        <v>-4.45985436</v>
       </c>
       <c r="Q92">
-        <v>-3.982516399999999</v>
+        <v>-4.03585436</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.749817489562572</v>
+        <v>1.939152766180636</v>
       </c>
       <c r="T92">
-        <v>8.372472136262923</v>
+        <v>9.302746818069915</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02871938359347326</v>
+        <v>0.02840378597156696</v>
       </c>
       <c r="W92">
-        <v>0.229027969348659</v>
+        <v>0.2291023872679045</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.08205538169563786</v>
+        <v>0.08115367420447706</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.3830069213700503</v>
+        <v>0.3849069213700503</v>
       </c>
       <c r="C93">
-        <v>-12.13834734964625</v>
+        <v>-12.57857000293012</v>
       </c>
       <c r="D93">
-        <v>16.45965265035375</v>
+        <v>16.36742999706988</v>
       </c>
       <c r="E93">
-        <v>31.668</v>
+        <v>32.016</v>
       </c>
       <c r="F93">
-        <v>31.668</v>
+        <v>32.016</v>
       </c>
       <c r="G93">
         <v>3.07</v>
@@ -8907,37 +8907,37 @@
         <v>0.606</v>
       </c>
       <c r="M93">
-        <v>7.4673144</v>
+        <v>7.5493728</v>
       </c>
       <c r="N93">
-        <v>-6.8613144</v>
+        <v>-6.9433728</v>
       </c>
       <c r="O93">
-        <v>-2.40146004</v>
+        <v>-2.43018048</v>
       </c>
       <c r="P93">
-        <v>-4.45985436</v>
+        <v>-4.51319232</v>
       </c>
       <c r="Q93">
-        <v>-4.03585436</v>
+        <v>-4.08919232</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.939152766180636</v>
+        <v>2.175821861953215</v>
       </c>
       <c r="T93">
-        <v>9.302746818069915</v>
+        <v>10.46559017032866</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02840378597156696</v>
+        <v>0.0280950491675282</v>
       </c>
       <c r="W93">
-        <v>0.2291023872679045</v>
+        <v>0.2291751874062969</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.08115367420447706</v>
+        <v>0.08027156905008059</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.3849069213700503</v>
+        <v>0.3868069213700502</v>
       </c>
       <c r="C94">
-        <v>-12.57857000293012</v>
+        <v>-13.01776497595146</v>
       </c>
       <c r="D94">
-        <v>16.36742999706988</v>
+        <v>16.27623502404854</v>
       </c>
       <c r="E94">
-        <v>32.016</v>
+        <v>32.364</v>
       </c>
       <c r="F94">
-        <v>32.016</v>
+        <v>32.364</v>
       </c>
       <c r="G94">
         <v>3.07</v>
@@ -8989,37 +8989,37 @@
         <v>0.606</v>
       </c>
       <c r="M94">
-        <v>7.5493728</v>
+        <v>7.6314312</v>
       </c>
       <c r="N94">
-        <v>-6.9433728</v>
+        <v>-7.0254312</v>
       </c>
       <c r="O94">
-        <v>-2.43018048</v>
+        <v>-2.45890092</v>
       </c>
       <c r="P94">
-        <v>-4.51319232</v>
+        <v>-4.56653028</v>
       </c>
       <c r="Q94">
-        <v>-4.08919232</v>
+        <v>-4.14253028</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>2.175821861953215</v>
+        <v>2.480110699375104</v>
       </c>
       <c r="T94">
-        <v>10.46559017032866</v>
+        <v>11.96067448037561</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.0280950491675282</v>
+        <v>0.02779295186465155</v>
       </c>
       <c r="W94">
-        <v>0.2291751874062969</v>
+        <v>0.2292464219503152</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.08027156905008059</v>
+        <v>0.07940843389900443</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3868069213700502</v>
+        <v>0.3887069213700503</v>
       </c>
       <c r="C95">
-        <v>-13.01776497595146</v>
+        <v>-13.45594935141444</v>
       </c>
       <c r="D95">
-        <v>16.27623502404854</v>
+        <v>16.18605064858556</v>
       </c>
       <c r="E95">
-        <v>32.364</v>
+        <v>32.712</v>
       </c>
       <c r="F95">
-        <v>32.364</v>
+        <v>32.712</v>
       </c>
       <c r="G95">
         <v>3.07</v>
@@ -9071,37 +9071,37 @@
         <v>0.606</v>
       </c>
       <c r="M95">
-        <v>7.6314312</v>
+        <v>7.713489599999999</v>
       </c>
       <c r="N95">
-        <v>-7.0254312</v>
+        <v>-7.107489599999999</v>
       </c>
       <c r="O95">
-        <v>-2.45890092</v>
+        <v>-2.487621359999999</v>
       </c>
       <c r="P95">
-        <v>-4.56653028</v>
+        <v>-4.61986824</v>
       </c>
       <c r="Q95">
-        <v>-4.14253028</v>
+        <v>-4.195868239999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>2.480110699375104</v>
+        <v>2.885829149270955</v>
       </c>
       <c r="T95">
-        <v>11.96067448037561</v>
+        <v>13.95412022710488</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02779295186465155</v>
+        <v>0.02749728216396377</v>
       </c>
       <c r="W95">
-        <v>0.2292464219503152</v>
+        <v>0.2293161408657374</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.07940843389900443</v>
+        <v>0.07856366332561071</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3887069213700503</v>
+        <v>0.3906069213700503</v>
       </c>
       <c r="C96">
-        <v>-13.45594935141444</v>
+        <v>-13.89313983549788</v>
       </c>
       <c r="D96">
-        <v>16.18605064858556</v>
+        <v>16.09686016450212</v>
       </c>
       <c r="E96">
-        <v>32.712</v>
+        <v>33.06</v>
       </c>
       <c r="F96">
-        <v>32.712</v>
+        <v>33.06</v>
       </c>
       <c r="G96">
         <v>3.07</v>
@@ -9153,37 +9153,37 @@
         <v>0.606</v>
       </c>
       <c r="M96">
-        <v>7.713489599999999</v>
+        <v>7.795548000000001</v>
       </c>
       <c r="N96">
-        <v>-7.107489599999999</v>
+        <v>-7.189548000000001</v>
       </c>
       <c r="O96">
-        <v>-2.487621359999999</v>
+        <v>-2.5163418</v>
       </c>
       <c r="P96">
-        <v>-4.61986824</v>
+        <v>-4.673206200000001</v>
       </c>
       <c r="Q96">
-        <v>-4.195868239999999</v>
+        <v>-4.249206200000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>2.885829149270955</v>
+        <v>3.453834979125149</v>
       </c>
       <c r="T96">
-        <v>13.95412022710488</v>
+        <v>16.74494427252587</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02749728216396377</v>
+        <v>0.02720783708855362</v>
       </c>
       <c r="W96">
-        <v>0.2293161408657374</v>
+        <v>0.2293843920145191</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.07856366332561071</v>
+        <v>0.07773667739586743</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3906069213700503</v>
+        <v>0.3925069213700503</v>
       </c>
       <c r="C97">
-        <v>-13.89313983549788</v>
+        <v>-14.32935276817225</v>
       </c>
       <c r="D97">
-        <v>16.09686016450212</v>
+        <v>16.00864723182775</v>
       </c>
       <c r="E97">
-        <v>33.06</v>
+        <v>33.408</v>
       </c>
       <c r="F97">
-        <v>33.06</v>
+        <v>33.408</v>
       </c>
       <c r="G97">
         <v>3.07</v>
@@ -9235,37 +9235,37 @@
         <v>0.606</v>
       </c>
       <c r="M97">
-        <v>7.795548000000001</v>
+        <v>7.8776064</v>
       </c>
       <c r="N97">
-        <v>-7.189548000000001</v>
+        <v>-7.2716064</v>
       </c>
       <c r="O97">
-        <v>-2.5163418</v>
+        <v>-2.54506224</v>
       </c>
       <c r="P97">
-        <v>-4.673206200000001</v>
+        <v>-4.72654416</v>
       </c>
       <c r="Q97">
-        <v>-4.249206200000001</v>
+        <v>-4.30254416</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>3.453834979125149</v>
+        <v>4.305843723906437</v>
       </c>
       <c r="T97">
-        <v>16.74494427252587</v>
+        <v>20.93118034065734</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.02720783708855362</v>
+        <v>0.02692442211888119</v>
       </c>
       <c r="W97">
-        <v>0.2293843920145191</v>
+        <v>0.2294512212643678</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.07773667739586743</v>
+        <v>0.07692692033966053</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3925069213700503</v>
+        <v>0.3944069213700503</v>
       </c>
       <c r="C98">
-        <v>-14.32935276817224</v>
+        <v>-14.76460413317938</v>
       </c>
       <c r="D98">
-        <v>16.00864723182775</v>
+        <v>15.92139586682062</v>
       </c>
       <c r="E98">
-        <v>33.40799999999999</v>
+        <v>33.75599999999999</v>
       </c>
       <c r="F98">
-        <v>33.40799999999999</v>
+        <v>33.75599999999999</v>
       </c>
       <c r="G98">
         <v>3.07</v>
@@ -9317,37 +9317,37 @@
         <v>0.606</v>
       </c>
       <c r="M98">
-        <v>7.877606399999999</v>
+        <v>7.959664799999999</v>
       </c>
       <c r="N98">
-        <v>-7.271606399999999</v>
+        <v>-7.353664799999999</v>
       </c>
       <c r="O98">
-        <v>-2.54506224</v>
+        <v>-2.573782679999999</v>
       </c>
       <c r="P98">
-        <v>-4.72654416</v>
+        <v>-4.77988212</v>
       </c>
       <c r="Q98">
-        <v>-4.302544159999999</v>
+        <v>-4.35588212</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>4.305843723906426</v>
+        <v>5.725858298541901</v>
       </c>
       <c r="T98">
-        <v>20.93118034065728</v>
+        <v>27.90824045420971</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02692442211888119</v>
+        <v>0.02664685075683087</v>
       </c>
       <c r="W98">
-        <v>0.2294512212643678</v>
+        <v>0.2295166725915393</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.07692692033966053</v>
+        <v>0.07613385930523109</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3944069213700503</v>
+        <v>0.3963069213700503</v>
       </c>
       <c r="C99">
-        <v>-14.76460413317938</v>
+        <v>-15.19890956768754</v>
       </c>
       <c r="D99">
-        <v>15.92139586682062</v>
+        <v>15.83509043231246</v>
       </c>
       <c r="E99">
-        <v>33.75599999999999</v>
+        <v>34.104</v>
       </c>
       <c r="F99">
-        <v>33.75599999999999</v>
+        <v>34.104</v>
       </c>
       <c r="G99">
         <v>3.07</v>
@@ -9399,37 +9399,37 @@
         <v>0.606</v>
       </c>
       <c r="M99">
-        <v>7.959664799999999</v>
+        <v>8.0417232</v>
       </c>
       <c r="N99">
-        <v>-7.353664799999999</v>
+        <v>-7.4357232</v>
       </c>
       <c r="O99">
-        <v>-2.573782679999999</v>
+        <v>-2.60250312</v>
       </c>
       <c r="P99">
-        <v>-4.77988212</v>
+        <v>-4.83322008</v>
       </c>
       <c r="Q99">
-        <v>-4.35588212</v>
+        <v>-4.40922008</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>5.725858298541901</v>
+        <v>8.565887447812852</v>
       </c>
       <c r="T99">
-        <v>27.90824045420971</v>
+        <v>41.86236068131457</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02664685075683087</v>
+        <v>0.02637494411645504</v>
       </c>
       <c r="W99">
-        <v>0.2295166725915393</v>
+        <v>0.2295807881773399</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.07613385930523109</v>
+        <v>0.0753569831898715</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3963069213700503</v>
+        <v>0.3982069213700503</v>
       </c>
       <c r="C100">
-        <v>-15.19890956768754</v>
+        <v>-15.63228437163415</v>
       </c>
       <c r="D100">
-        <v>15.83509043231246</v>
+        <v>15.74971562836585</v>
       </c>
       <c r="E100">
-        <v>34.104</v>
+        <v>34.452</v>
       </c>
       <c r="F100">
-        <v>34.104</v>
+        <v>34.452</v>
       </c>
       <c r="G100">
         <v>3.07</v>
@@ -9481,37 +9481,37 @@
         <v>0.606</v>
       </c>
       <c r="M100">
-        <v>8.0417232</v>
+        <v>8.123781599999999</v>
       </c>
       <c r="N100">
-        <v>-7.4357232</v>
+        <v>-7.517781599999999</v>
       </c>
       <c r="O100">
-        <v>-2.60250312</v>
+        <v>-2.63122356</v>
       </c>
       <c r="P100">
-        <v>-4.83322008</v>
+        <v>-4.88655804</v>
       </c>
       <c r="Q100">
-        <v>-4.40922008</v>
+        <v>-4.462558039999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>8.565887447812852</v>
+        <v>17.0859748956257</v>
       </c>
       <c r="T100">
-        <v>41.86236068131457</v>
+        <v>83.72472136262914</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02637494411645504</v>
+        <v>0.02610853053952115</v>
       </c>
       <c r="W100">
-        <v>0.2295807881773399</v>
+        <v>0.2296436084987809</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.0753569831898715</v>
+        <v>0.07459580154148904</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3982069213700503</v>
-      </c>
-      <c r="C101">
-        <v>-15.63228437163415</v>
-      </c>
-      <c r="D101">
-        <v>15.74971562836585</v>
-      </c>
-      <c r="E101">
-        <v>34.452</v>
-      </c>
-      <c r="F101">
-        <v>34.452</v>
-      </c>
-      <c r="G101">
-        <v>3.07</v>
-      </c>
-      <c r="H101">
-        <v>34.8</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1.03</v>
-      </c>
-      <c r="K101">
-        <v>0.424</v>
-      </c>
-      <c r="L101">
-        <v>0.606</v>
-      </c>
-      <c r="M101">
-        <v>8.123781599999999</v>
-      </c>
-      <c r="N101">
-        <v>-7.517781599999999</v>
-      </c>
-      <c r="O101">
-        <v>-2.63122356</v>
-      </c>
-      <c r="P101">
-        <v>-4.88655804</v>
-      </c>
-      <c r="Q101">
-        <v>-4.462558039999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>17.0859748956257</v>
-      </c>
-      <c r="T101">
-        <v>83.72472136262914</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02610853053952115</v>
-      </c>
-      <c r="W101">
-        <v>0.2296436084987809</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.07459580154148904</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
